--- a/Genesis.xlsx
+++ b/Genesis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rohan\Desktop\Dashboard\Genesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4132B58C-5D21-4438-BE4D-14F64832C1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A5EA58-1B19-42BB-861F-6D1B38C578A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10341" uniqueCount="1452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10341" uniqueCount="1451">
   <si>
     <t>S.no</t>
   </si>
@@ -2824,9 +2824,6 @@
     <t>Safesphere Technologies Private Limited</t>
   </si>
   <si>
-    <t>Rajesthan</t>
-  </si>
-  <si>
     <t>jaipur</t>
   </si>
   <si>
@@ -3008,9 +3005,6 @@
   </si>
   <si>
     <t>Frayit Technologies Private Limited</t>
-  </si>
-  <si>
-    <t>Madhy Pradesh</t>
   </si>
   <si>
     <t>indore</t>
@@ -4407,6 +4401,9 @@
   </si>
   <si>
     <t>Teerthanker Mahaveer University Business Incubation Centre</t>
+  </si>
+  <si>
+    <t>Rajasthan</t>
   </si>
 </sst>
 </file>
@@ -5063,13 +5060,13 @@
         <v>49</v>
       </c>
       <c r="F3" s="17" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G3" s="17" t="s">
         <v>929</v>
       </c>
-      <c r="G3" s="17" t="s">
-        <v>930</v>
-      </c>
       <c r="H3" s="17" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I3" s="17" t="s">
         <v>84</v>
@@ -5122,19 +5119,19 @@
         <v>52</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F4" s="17" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G4" s="17" t="s">
         <v>929</v>
       </c>
-      <c r="G4" s="17" t="s">
-        <v>930</v>
-      </c>
       <c r="H4" s="17" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I4" s="17" t="s">
         <v>84</v>
@@ -5187,19 +5184,19 @@
         <v>52</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F5" s="17" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G5" s="17" t="s">
         <v>929</v>
       </c>
-      <c r="G5" s="17" t="s">
-        <v>930</v>
-      </c>
       <c r="H5" s="17" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I5" s="17" t="s">
         <v>84</v>
@@ -5252,25 +5249,25 @@
         <v>52</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F6" s="17" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G6" s="17" t="s">
         <v>929</v>
       </c>
-      <c r="G6" s="17" t="s">
-        <v>930</v>
-      </c>
       <c r="H6" s="17" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I6" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="K6" s="17" t="s">
         <v>45</v>
@@ -5317,19 +5314,19 @@
         <v>52</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F7" s="17" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G7" s="17" t="s">
         <v>929</v>
       </c>
-      <c r="G7" s="17" t="s">
-        <v>930</v>
-      </c>
       <c r="H7" s="17" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>31</v>
@@ -5379,7 +5376,7 @@
         <v>908</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>26</v>
@@ -5444,7 +5441,7 @@
         <v>908</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>39</v>
@@ -5509,7 +5506,7 @@
         <v>908</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>47</v>
@@ -5574,10 +5571,10 @@
         <v>923</v>
       </c>
       <c r="C11" s="17" t="s">
+        <v>935</v>
+      </c>
+      <c r="D11" s="17" t="s">
         <v>936</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>937</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>28</v>
@@ -5589,7 +5586,7 @@
         <v>42</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>31</v>
@@ -5639,10 +5636,10 @@
         <v>923</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>49</v>
@@ -5651,10 +5648,10 @@
         <v>77</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>84</v>
@@ -5704,10 +5701,10 @@
         <v>923</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>49</v>
@@ -5716,10 +5713,10 @@
         <v>77</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>31</v>
@@ -5971,7 +5968,7 @@
         <v>49</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>70</v>
@@ -6036,7 +6033,7 @@
         <v>49</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>70</v>
@@ -6609,7 +6606,7 @@
         <v>74</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>49</v>
@@ -6618,10 +6615,10 @@
         <v>91</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>31</v>
@@ -6674,7 +6671,7 @@
         <v>74</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="E28" s="17" t="s">
         <v>49</v>
@@ -6739,7 +6736,7 @@
         <v>74</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>49</v>
@@ -6751,7 +6748,7 @@
         <v>362</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>31</v>
@@ -6804,7 +6801,7 @@
         <v>74</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>49</v>
@@ -6813,10 +6810,10 @@
         <v>55</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="I30" s="17" t="s">
         <v>51</v>
@@ -6867,7 +6864,7 @@
         <v>74</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E31" s="17" t="s">
         <v>49</v>
@@ -6876,10 +6873,10 @@
         <v>348</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="I31" s="4" t="s">
         <v>31</v>
@@ -7192,7 +7189,7 @@
         <v>113</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E36" s="17" t="s">
         <v>49</v>
@@ -7257,7 +7254,7 @@
         <v>113</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E37" s="17" t="s">
         <v>28</v>
@@ -7712,7 +7709,7 @@
         <v>125</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>49</v>
@@ -7721,10 +7718,10 @@
         <v>110</v>
       </c>
       <c r="G44" s="17" t="s">
+        <v>955</v>
+      </c>
+      <c r="H44" s="17" t="s">
         <v>956</v>
-      </c>
-      <c r="H44" s="17" t="s">
-        <v>957</v>
       </c>
       <c r="I44" s="17" t="s">
         <v>84</v>
@@ -7777,7 +7774,7 @@
         <v>125</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>49</v>
@@ -7789,7 +7786,7 @@
         <v>32</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>31</v>
@@ -7842,7 +7839,7 @@
         <v>125</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>49</v>
@@ -7854,7 +7851,7 @@
         <v>32</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>31</v>
@@ -7905,7 +7902,7 @@
         <v>125</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>49</v>
@@ -7917,7 +7914,7 @@
         <v>32</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>31</v>
@@ -7970,7 +7967,7 @@
         <v>125</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>49</v>
@@ -7982,7 +7979,7 @@
         <v>32</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>31</v>
@@ -8032,10 +8029,10 @@
         <v>923</v>
       </c>
       <c r="C49" s="17" t="s">
+        <v>964</v>
+      </c>
+      <c r="D49" s="17" t="s">
         <v>965</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>966</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>49</v>
@@ -8044,10 +8041,10 @@
         <v>77</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>31</v>
@@ -8056,7 +8053,7 @@
         <v>247</v>
       </c>
       <c r="K49" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L49" s="13" t="s">
         <v>247</v>
@@ -8097,10 +8094,10 @@
         <v>923</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E50" s="17" t="s">
         <v>49</v>
@@ -8109,10 +8106,10 @@
         <v>282</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="I50" s="17" t="s">
         <v>84</v>
@@ -8162,22 +8159,22 @@
         <v>923</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F51" s="17" t="s">
+        <v>971</v>
+      </c>
+      <c r="G51" s="17" t="s">
         <v>972</v>
       </c>
-      <c r="G51" s="17" t="s">
-        <v>973</v>
-      </c>
       <c r="H51" s="17" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="I51" s="17" t="s">
         <v>84</v>
@@ -8186,7 +8183,7 @@
         <v>794</v>
       </c>
       <c r="K51" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L51" s="13" t="s">
         <v>794</v>
@@ -8227,10 +8224,10 @@
         <v>923</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>49</v>
@@ -8239,10 +8236,10 @@
         <v>181</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="I52" s="17" t="s">
         <v>84</v>
@@ -8292,10 +8289,10 @@
         <v>923</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>49</v>
@@ -8304,10 +8301,10 @@
         <v>181</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="I53" s="17" t="s">
         <v>84</v>
@@ -8357,10 +8354,10 @@
         <v>923</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E54" s="17" t="s">
         <v>49</v>
@@ -8369,10 +8366,10 @@
         <v>282</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="I54" s="17" t="s">
         <v>84</v>
@@ -8620,7 +8617,7 @@
         <v>144</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E58" s="17" t="s">
         <v>49</v>
@@ -8629,10 +8626,10 @@
         <v>147</v>
       </c>
       <c r="G58" s="17" t="s">
+        <v>979</v>
+      </c>
+      <c r="H58" s="17" t="s">
         <v>980</v>
-      </c>
-      <c r="H58" s="17" t="s">
-        <v>981</v>
       </c>
       <c r="I58" s="17" t="s">
         <v>84</v>
@@ -8685,7 +8682,7 @@
         <v>144</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E59" s="17" t="s">
         <v>49</v>
@@ -8694,10 +8691,10 @@
         <v>91</v>
       </c>
       <c r="G59" s="17" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H59" s="17" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>31</v>
@@ -9110,7 +9107,7 @@
         <v>155</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="E66" s="17" t="s">
         <v>49</v>
@@ -9119,10 +9116,10 @@
         <v>96</v>
       </c>
       <c r="G66" s="17" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H66" s="17" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>31</v>
@@ -9169,7 +9166,7 @@
         <v>155</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E67" s="17" t="s">
         <v>49</v>
@@ -9178,10 +9175,10 @@
         <v>96</v>
       </c>
       <c r="G67" s="17" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H67" s="17" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>31</v>
@@ -9226,7 +9223,7 @@
         <v>155</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E68" s="17" t="s">
         <v>49</v>
@@ -9235,10 +9232,10 @@
         <v>96</v>
       </c>
       <c r="G68" s="17" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H68" s="17" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>31</v>
@@ -9283,7 +9280,7 @@
         <v>155</v>
       </c>
       <c r="D69" s="17" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="E69" s="17" t="s">
         <v>28</v>
@@ -9292,10 +9289,10 @@
         <v>96</v>
       </c>
       <c r="G69" s="17" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H69" s="17" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>31</v>
@@ -9336,7 +9333,7 @@
         <v>155</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E70" s="17" t="s">
         <v>28</v>
@@ -9345,10 +9342,10 @@
         <v>96</v>
       </c>
       <c r="G70" s="17" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H70" s="17" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>31</v>
@@ -9398,7 +9395,7 @@
       <c r="E71" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="F71" s="17" t="s">
         <v>171</v>
       </c>
       <c r="G71" s="4" t="s">
@@ -9523,19 +9520,19 @@
         <v>168</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E73" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F73" s="17" t="s">
-        <v>991</v>
+        <v>171</v>
       </c>
       <c r="G73" s="17" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="H73" s="17" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>31</v>
@@ -9586,19 +9583,19 @@
         <v>168</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="E74" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F74" s="17" t="s">
-        <v>991</v>
+        <v>171</v>
       </c>
       <c r="G74" s="17" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="H74" s="17" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>31</v>
@@ -10234,7 +10231,7 @@
         <v>195</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="E84" s="17" t="s">
         <v>49</v>
@@ -10295,7 +10292,7 @@
         <v>195</v>
       </c>
       <c r="D85" s="17" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="E85" s="17" t="s">
         <v>49</v>
@@ -10304,10 +10301,10 @@
         <v>110</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="I85" s="17" t="s">
         <v>84</v>
@@ -10360,7 +10357,7 @@
         <v>195</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="E86" s="17" t="s">
         <v>49</v>
@@ -10369,10 +10366,10 @@
         <v>110</v>
       </c>
       <c r="G86" s="15" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="H86" s="15" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="I86" s="4" t="s">
         <v>31</v>
@@ -10425,7 +10422,7 @@
         <v>195</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="E87" s="17" t="s">
         <v>49</v>
@@ -10483,22 +10480,22 @@
         <v>923</v>
       </c>
       <c r="C88" s="17" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="E88" s="17" t="s">
         <v>28</v>
       </c>
       <c r="F88" s="17" t="s">
-        <v>991</v>
+        <v>171</v>
       </c>
       <c r="G88" s="17" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="H88" s="17" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="I88" s="4" t="s">
         <v>31</v>
@@ -10548,22 +10545,22 @@
         <v>923</v>
       </c>
       <c r="C89" s="17" t="s">
+        <v>999</v>
+      </c>
+      <c r="D89" s="17" t="s">
         <v>1001</v>
-      </c>
-      <c r="D89" s="17" t="s">
-        <v>1003</v>
       </c>
       <c r="E89" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F89" s="17" t="s">
-        <v>991</v>
+        <v>171</v>
       </c>
       <c r="G89" s="17" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="H89" s="17" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>31</v>
@@ -10572,7 +10569,7 @@
         <v>794</v>
       </c>
       <c r="K89" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L89" s="13" t="s">
         <v>794</v>
@@ -10613,22 +10610,22 @@
         <v>923</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E90" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F90" s="17" t="s">
-        <v>991</v>
+        <v>171</v>
       </c>
       <c r="G90" s="17" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="H90" s="17" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="I90" s="4" t="s">
         <v>31</v>
@@ -10678,22 +10675,22 @@
         <v>923</v>
       </c>
       <c r="C91" s="17" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="D91" s="17" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="E91" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F91" s="17" t="s">
-        <v>991</v>
+        <v>171</v>
       </c>
       <c r="G91" s="17" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="H91" s="17" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="I91" s="17" t="s">
         <v>84</v>
@@ -10743,7 +10740,7 @@
         <v>908</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>207</v>
@@ -10751,7 +10748,7 @@
       <c r="E92" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F92" s="4" t="s">
+      <c r="F92" s="17" t="s">
         <v>171</v>
       </c>
       <c r="G92" s="4" t="s">
@@ -10808,7 +10805,7 @@
         <v>908</v>
       </c>
       <c r="C93" s="17" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>210</v>
@@ -10816,7 +10813,7 @@
       <c r="E93" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F93" s="4" t="s">
+      <c r="F93" s="17" t="s">
         <v>171</v>
       </c>
       <c r="G93" s="4" t="s">
@@ -10871,10 +10868,10 @@
         <v>923</v>
       </c>
       <c r="C94" s="17" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E94" s="17" t="s">
         <v>49</v>
@@ -10883,10 +10880,10 @@
         <v>141</v>
       </c>
       <c r="G94" s="17" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="H94" s="17" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="I94" s="17" t="s">
         <v>84</v>
@@ -10936,10 +10933,10 @@
         <v>923</v>
       </c>
       <c r="C95" s="17" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="E95" s="17" t="s">
         <v>49</v>
@@ -10948,10 +10945,10 @@
         <v>55</v>
       </c>
       <c r="G95" s="17" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="H95" s="17" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="I95" s="4" t="s">
         <v>31</v>
@@ -10999,22 +10996,22 @@
         <v>923</v>
       </c>
       <c r="C96" s="17" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="E96" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F96" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G96" s="17" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="H96" s="17" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="I96" s="17" t="s">
         <v>84</v>
@@ -11064,10 +11061,10 @@
         <v>923</v>
       </c>
       <c r="C97" s="17" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="D97" s="17" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="E97" s="17" t="s">
         <v>49</v>
@@ -11076,10 +11073,10 @@
         <v>96</v>
       </c>
       <c r="G97" s="17" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="H97" s="17" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="I97" s="17" t="s">
         <v>84</v>
@@ -11088,7 +11085,7 @@
         <v>794</v>
       </c>
       <c r="K97" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L97" s="13" t="s">
         <v>794</v>
@@ -11129,7 +11126,7 @@
         <v>908</v>
       </c>
       <c r="C98" s="17" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>214</v>
@@ -11194,7 +11191,7 @@
         <v>908</v>
       </c>
       <c r="C99" s="17" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>217</v>
@@ -11259,7 +11256,7 @@
         <v>908</v>
       </c>
       <c r="C100" s="17" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>219</v>
@@ -11324,7 +11321,7 @@
         <v>908</v>
       </c>
       <c r="C101" s="17" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>222</v>
@@ -11398,7 +11395,7 @@
         <v>28</v>
       </c>
       <c r="F102" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G102" s="4" t="s">
         <v>228</v>
@@ -11636,7 +11633,7 @@
         <v>225</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E106" s="17" t="s">
         <v>49</v>
@@ -11645,10 +11642,10 @@
         <v>511</v>
       </c>
       <c r="G106" s="17" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="H106" s="17" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="I106" s="17" t="s">
         <v>84</v>
@@ -11657,7 +11654,7 @@
         <v>794</v>
       </c>
       <c r="K106" s="17" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="L106" s="13" t="s">
         <v>794</v>
@@ -11701,7 +11698,7 @@
         <v>225</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="E107" s="17" t="s">
         <v>49</v>
@@ -11710,10 +11707,10 @@
         <v>77</v>
       </c>
       <c r="G107" s="17" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="H107" s="17" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>31</v>
@@ -11722,7 +11719,7 @@
         <v>916</v>
       </c>
       <c r="K107" s="17" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="L107" s="13" t="s">
         <v>916</v>
@@ -11766,7 +11763,7 @@
         <v>225</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="E108" s="17" t="s">
         <v>49</v>
@@ -11778,7 +11775,7 @@
         <v>362</v>
       </c>
       <c r="H108" s="17" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="I108" s="4" t="s">
         <v>31</v>
@@ -11787,7 +11784,7 @@
         <v>610</v>
       </c>
       <c r="K108" s="17" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="L108" s="13" t="s">
         <v>610</v>
@@ -11831,7 +11828,7 @@
         <v>225</v>
       </c>
       <c r="D109" s="17" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="E109" s="17" t="s">
         <v>49</v>
@@ -11843,7 +11840,7 @@
         <v>362</v>
       </c>
       <c r="H109" s="17" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="I109" s="4" t="s">
         <v>31</v>
@@ -11852,7 +11849,7 @@
         <v>916</v>
       </c>
       <c r="K109" s="17" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="L109" s="13" t="s">
         <v>916</v>
@@ -11896,7 +11893,7 @@
         <v>225</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="E110" s="17" t="s">
         <v>49</v>
@@ -11905,10 +11902,10 @@
         <v>77</v>
       </c>
       <c r="G110" s="17" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="H110" s="17" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="I110" s="17" t="s">
         <v>84</v>
@@ -11917,7 +11914,7 @@
         <v>794</v>
       </c>
       <c r="K110" s="17" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="L110" s="13" t="s">
         <v>247</v>
@@ -11961,7 +11958,7 @@
         <v>225</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="E111" s="17" t="s">
         <v>49</v>
@@ -11970,10 +11967,10 @@
         <v>319</v>
       </c>
       <c r="G111" s="17" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="H111" s="17" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="I111" s="17" t="s">
         <v>84</v>
@@ -11982,7 +11979,7 @@
         <v>915</v>
       </c>
       <c r="K111" s="17" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="L111" s="13" t="s">
         <v>915</v>
@@ -12023,10 +12020,10 @@
         <v>923</v>
       </c>
       <c r="C112" s="17" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="E112" s="17" t="s">
         <v>28</v>
@@ -12035,10 +12032,10 @@
         <v>29</v>
       </c>
       <c r="G112" s="17" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="H112" s="17" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="I112" s="17" t="s">
         <v>84</v>
@@ -12088,10 +12085,10 @@
         <v>923</v>
       </c>
       <c r="C113" s="17" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="E113" s="17" t="s">
         <v>49</v>
@@ -12100,10 +12097,10 @@
         <v>29</v>
       </c>
       <c r="G113" s="17" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="H113" s="17" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="I113" s="4" t="s">
         <v>31</v>
@@ -12153,10 +12150,10 @@
         <v>923</v>
       </c>
       <c r="C114" s="17" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="E114" s="17" t="s">
         <v>49</v>
@@ -12165,10 +12162,10 @@
         <v>96</v>
       </c>
       <c r="G114" s="17" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="H114" s="17" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="I114" s="17" t="s">
         <v>84</v>
@@ -12218,7 +12215,7 @@
         <v>908</v>
       </c>
       <c r="C115" s="17" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>237</v>
@@ -12283,7 +12280,7 @@
         <v>908</v>
       </c>
       <c r="C116" s="17" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>240</v>
@@ -12348,7 +12345,7 @@
         <v>908</v>
       </c>
       <c r="C117" s="17" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>242</v>
@@ -12741,7 +12738,7 @@
         <v>244</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="E123" s="17" t="s">
         <v>28</v>
@@ -12806,7 +12803,7 @@
         <v>244</v>
       </c>
       <c r="D124" s="17" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="E124" s="17" t="s">
         <v>49</v>
@@ -12815,10 +12812,10 @@
         <v>77</v>
       </c>
       <c r="G124" s="17" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H124" s="17" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="I124" s="4" t="s">
         <v>31</v>
@@ -12871,7 +12868,7 @@
         <v>244</v>
       </c>
       <c r="D125" s="17" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="E125" s="17" t="s">
         <v>49</v>
@@ -12880,7 +12877,7 @@
         <v>77</v>
       </c>
       <c r="G125" s="17" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>384</v>
@@ -12936,7 +12933,7 @@
         <v>244</v>
       </c>
       <c r="D126" s="17" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="E126" s="17" t="s">
         <v>49</v>
@@ -13001,7 +12998,7 @@
         <v>244</v>
       </c>
       <c r="D127" s="17" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="E127" s="17" t="s">
         <v>28</v>
@@ -13010,10 +13007,10 @@
         <v>82</v>
       </c>
       <c r="G127" s="17" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="H127" s="17" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="I127" s="17" t="s">
         <v>84</v>
@@ -13066,19 +13063,19 @@
         <v>244</v>
       </c>
       <c r="D128" s="17" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="E128" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F128" s="17" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G128" s="17" t="s">
         <v>929</v>
       </c>
-      <c r="G128" s="17" t="s">
-        <v>930</v>
-      </c>
       <c r="H128" s="17" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I128" s="4" t="s">
         <v>31</v>
@@ -13331,7 +13328,7 @@
       <c r="E132" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F132" s="4" t="s">
+      <c r="F132" s="17" t="s">
         <v>171</v>
       </c>
       <c r="G132" s="4" t="s">
@@ -13564,7 +13561,7 @@
         <v>258</v>
       </c>
       <c r="D136" s="17" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E136" s="17" t="s">
         <v>49</v>
@@ -13629,7 +13626,7 @@
         <v>258</v>
       </c>
       <c r="D137" s="17" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="E137" s="17" t="s">
         <v>49</v>
@@ -13638,10 +13635,10 @@
         <v>265</v>
       </c>
       <c r="G137" s="17" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="H137" s="17" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="I137" s="4" t="s">
         <v>31</v>
@@ -13694,19 +13691,19 @@
         <v>258</v>
       </c>
       <c r="D138" s="17" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="E138" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F138" s="17" t="s">
-        <v>991</v>
+        <v>171</v>
       </c>
       <c r="G138" s="17" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="H138" s="17" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="I138" s="4" t="s">
         <v>31</v>
@@ -13759,7 +13756,7 @@
         <v>258</v>
       </c>
       <c r="D139" s="17" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E139" s="17" t="s">
         <v>49</v>
@@ -13768,10 +13765,10 @@
         <v>65</v>
       </c>
       <c r="G139" s="17" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="H139" s="17" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="I139" s="4" t="s">
         <v>31</v>
@@ -13824,7 +13821,7 @@
         <v>258</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="E140" s="17" t="s">
         <v>49</v>
@@ -13833,10 +13830,10 @@
         <v>77</v>
       </c>
       <c r="G140" s="17" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H140" s="17" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="I140" s="4" t="s">
         <v>31</v>
@@ -13889,7 +13886,7 @@
         <v>258</v>
       </c>
       <c r="D141" s="17" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E141" s="17" t="s">
         <v>49</v>
@@ -13898,10 +13895,10 @@
         <v>50</v>
       </c>
       <c r="G141" s="17" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="H141" s="17" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="I141" s="4" t="s">
         <v>31</v>
@@ -14474,7 +14471,7 @@
         <v>285</v>
       </c>
       <c r="D150" s="17" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="E150" s="17" t="s">
         <v>49</v>
@@ -14483,10 +14480,10 @@
         <v>29</v>
       </c>
       <c r="G150" s="17" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="H150" s="17" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="I150" s="4" t="s">
         <v>31</v>
@@ -14539,7 +14536,7 @@
         <v>285</v>
       </c>
       <c r="D151" s="17" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="E151" s="17" t="s">
         <v>49</v>
@@ -14548,10 +14545,10 @@
         <v>29</v>
       </c>
       <c r="G151" s="17" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="H151" s="17" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="I151" s="4" t="s">
         <v>31</v>
@@ -14604,7 +14601,7 @@
         <v>285</v>
       </c>
       <c r="D152" s="17" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="E152" s="17" t="s">
         <v>49</v>
@@ -14613,10 +14610,10 @@
         <v>29</v>
       </c>
       <c r="G152" s="17" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="H152" s="17" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="I152" s="4" t="s">
         <v>31</v>
@@ -14669,7 +14666,7 @@
         <v>285</v>
       </c>
       <c r="D153" s="17" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="E153" s="17" t="s">
         <v>49</v>
@@ -14678,10 +14675,10 @@
         <v>29</v>
       </c>
       <c r="G153" s="17" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="H153" s="17" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="I153" s="4" t="s">
         <v>31</v>
@@ -14928,7 +14925,7 @@
       <c r="E157" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F157" s="4" t="s">
+      <c r="F157" s="17" t="s">
         <v>319</v>
       </c>
       <c r="G157" s="4" t="s">
@@ -14986,7 +14983,7 @@
         <v>306</v>
       </c>
       <c r="D158" s="17" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="E158" s="17" t="s">
         <v>28</v>
@@ -14995,10 +14992,10 @@
         <v>309</v>
       </c>
       <c r="G158" s="17" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="H158" s="17" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="I158" s="4" t="s">
         <v>31</v>
@@ -15051,7 +15048,7 @@
         <v>306</v>
       </c>
       <c r="D159" s="17" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="E159" s="17" t="s">
         <v>49</v>
@@ -15060,10 +15057,10 @@
         <v>309</v>
       </c>
       <c r="G159" s="17" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="H159" s="17" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="I159" s="17" t="s">
         <v>84</v>
@@ -15374,7 +15371,7 @@
         <v>321</v>
       </c>
       <c r="D164" s="17" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="E164" s="17" t="s">
         <v>28</v>
@@ -15383,10 +15380,10 @@
         <v>102</v>
       </c>
       <c r="G164" s="17" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="H164" s="17" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="I164" s="4" t="s">
         <v>31</v>
@@ -15439,7 +15436,7 @@
         <v>321</v>
       </c>
       <c r="D165" s="17" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="E165" s="17" t="s">
         <v>49</v>
@@ -15448,10 +15445,10 @@
         <v>102</v>
       </c>
       <c r="G165" s="17" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="H165" s="17" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="I165" s="4" t="s">
         <v>31</v>
@@ -15504,7 +15501,7 @@
         <v>321</v>
       </c>
       <c r="D166" s="17" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="E166" s="17" t="s">
         <v>49</v>
@@ -15513,10 +15510,10 @@
         <v>102</v>
       </c>
       <c r="G166" s="17" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="H166" s="17" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="I166" s="4" t="s">
         <v>31</v>
@@ -15569,7 +15566,7 @@
         <v>321</v>
       </c>
       <c r="D167" s="17" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="E167" s="17" t="s">
         <v>49</v>
@@ -15578,10 +15575,10 @@
         <v>102</v>
       </c>
       <c r="G167" s="17" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="H167" s="17" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="I167" s="4" t="s">
         <v>31</v>
@@ -15634,7 +15631,7 @@
         <v>321</v>
       </c>
       <c r="D168" s="17" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="E168" s="17" t="s">
         <v>49</v>
@@ -15643,10 +15640,10 @@
         <v>102</v>
       </c>
       <c r="G168" s="17" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="H168" s="17" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="I168" s="4" t="s">
         <v>31</v>
@@ -15769,7 +15766,7 @@
       <c r="E170" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F170" s="4" t="s">
+      <c r="F170" s="17" t="s">
         <v>171</v>
       </c>
       <c r="G170" s="4" t="s">
@@ -16150,7 +16147,7 @@
         <v>336</v>
       </c>
       <c r="D176" s="17" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="E176" s="17" t="s">
         <v>28</v>
@@ -16159,10 +16156,10 @@
         <v>77</v>
       </c>
       <c r="G176" s="17" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="H176" s="17" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="I176" s="17" t="s">
         <v>84</v>
@@ -16213,19 +16210,19 @@
         <v>336</v>
       </c>
       <c r="D177" s="17" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="E177" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F177" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G177" s="17" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="H177" s="17" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="I177" s="17" t="s">
         <v>84</v>
@@ -16343,7 +16340,7 @@
         <v>336</v>
       </c>
       <c r="D179" s="17" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="E179" s="17" t="s">
         <v>49</v>
@@ -16408,19 +16405,19 @@
         <v>336</v>
       </c>
       <c r="D180" s="17" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="E180" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F180" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G180" s="17" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="H180" s="17" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="I180" s="4" t="s">
         <v>31</v>
@@ -16473,7 +16470,7 @@
         <v>336</v>
       </c>
       <c r="D181" s="17" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="E181" s="17" t="s">
         <v>28</v>
@@ -16482,10 +16479,10 @@
         <v>319</v>
       </c>
       <c r="G181" s="17" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="H181" s="17" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I181" s="4" t="s">
         <v>31</v>
@@ -16983,7 +16980,7 @@
         <v>363</v>
       </c>
       <c r="D189" s="17" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="E189" s="17" t="s">
         <v>49</v>
@@ -17048,7 +17045,7 @@
         <v>363</v>
       </c>
       <c r="D190" s="17" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="E190" s="17" t="s">
         <v>49</v>
@@ -17113,7 +17110,7 @@
         <v>363</v>
       </c>
       <c r="D191" s="17" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="E191" s="17" t="s">
         <v>49</v>
@@ -17178,7 +17175,7 @@
         <v>363</v>
       </c>
       <c r="D192" s="17" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="E192" s="17" t="s">
         <v>28</v>
@@ -17243,7 +17240,7 @@
         <v>363</v>
       </c>
       <c r="D193" s="17" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="E193" s="17" t="s">
         <v>49</v>
@@ -17308,7 +17305,7 @@
         <v>363</v>
       </c>
       <c r="D194" s="17" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E194" s="17" t="s">
         <v>49</v>
@@ -17370,10 +17367,10 @@
         <v>923</v>
       </c>
       <c r="C195" s="17" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="D195" s="17" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="E195" s="17" t="s">
         <v>49</v>
@@ -17382,10 +17379,10 @@
         <v>358</v>
       </c>
       <c r="G195" s="17" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="H195" s="17" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="I195" s="17" t="s">
         <v>84</v>
@@ -17435,10 +17432,10 @@
         <v>923</v>
       </c>
       <c r="C196" s="17" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="D196" s="17" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="E196" s="17" t="s">
         <v>49</v>
@@ -17447,10 +17444,10 @@
         <v>358</v>
       </c>
       <c r="G196" s="17" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H196" s="17" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="I196" s="17" t="s">
         <v>84</v>
@@ -17500,10 +17497,10 @@
         <v>923</v>
       </c>
       <c r="C197" s="17" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="D197" s="17" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="E197" s="17" t="s">
         <v>28</v>
@@ -17512,10 +17509,10 @@
         <v>358</v>
       </c>
       <c r="G197" s="17" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H197" s="17" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="I197" s="17" t="s">
         <v>84</v>
@@ -17565,10 +17562,10 @@
         <v>923</v>
       </c>
       <c r="C198" s="17" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="D198" s="17" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="E198" s="17" t="s">
         <v>49</v>
@@ -17577,10 +17574,10 @@
         <v>358</v>
       </c>
       <c r="G198" s="17" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="H198" s="17" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="I198" s="17" t="s">
         <v>84</v>
@@ -17630,7 +17627,7 @@
         <v>908</v>
       </c>
       <c r="C199" s="17" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="D199" s="3" t="s">
         <v>380</v>
@@ -17638,7 +17635,7 @@
       <c r="E199" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F199" s="4" t="s">
+      <c r="F199" s="17" t="s">
         <v>171</v>
       </c>
       <c r="G199" s="4" t="s">
@@ -17695,7 +17692,7 @@
         <v>908</v>
       </c>
       <c r="C200" s="17" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>382</v>
@@ -17760,7 +17757,7 @@
         <v>908</v>
       </c>
       <c r="C201" s="17" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="D201" s="3" t="s">
         <v>385</v>
@@ -17769,7 +17766,7 @@
         <v>49</v>
       </c>
       <c r="F201" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G201" s="4" t="s">
         <v>70</v>
@@ -17825,7 +17822,7 @@
         <v>908</v>
       </c>
       <c r="C202" s="17" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="D202" s="3" t="s">
         <v>387</v>
@@ -17834,7 +17831,7 @@
         <v>49</v>
       </c>
       <c r="F202" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G202" s="4" t="s">
         <v>70</v>
@@ -18153,7 +18150,7 @@
         <v>389</v>
       </c>
       <c r="D207" s="17" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="E207" s="17" t="s">
         <v>49</v>
@@ -18162,10 +18159,10 @@
         <v>141</v>
       </c>
       <c r="G207" s="17" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H207" s="17" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="I207" s="17" t="s">
         <v>51</v>
@@ -18206,7 +18203,7 @@
         <v>389</v>
       </c>
       <c r="D208" s="17" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="E208" s="17" t="s">
         <v>28</v>
@@ -18215,10 +18212,10 @@
         <v>141</v>
       </c>
       <c r="G208" s="17" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H208" s="17" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="I208" s="17" t="s">
         <v>51</v>
@@ -18259,7 +18256,7 @@
         <v>389</v>
       </c>
       <c r="D209" s="17" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="E209" s="17" t="s">
         <v>49</v>
@@ -18268,10 +18265,10 @@
         <v>141</v>
       </c>
       <c r="G209" s="17" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H209" s="17" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="I209" s="17" t="s">
         <v>51</v>
@@ -18312,7 +18309,7 @@
         <v>389</v>
       </c>
       <c r="D210" s="17" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="E210" s="17" t="s">
         <v>49</v>
@@ -18321,10 +18318,10 @@
         <v>141</v>
       </c>
       <c r="G210" s="17" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H210" s="17" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="I210" s="17" t="s">
         <v>51</v>
@@ -18333,7 +18330,7 @@
         <v>794</v>
       </c>
       <c r="K210" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L210" s="13" t="s">
         <v>794</v>
@@ -18365,7 +18362,7 @@
         <v>389</v>
       </c>
       <c r="D211" s="17" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="E211" s="17" t="s">
         <v>49</v>
@@ -18374,10 +18371,10 @@
         <v>141</v>
       </c>
       <c r="G211" s="17" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H211" s="17" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="I211" s="17" t="s">
         <v>51</v>
@@ -18416,7 +18413,7 @@
         <v>389</v>
       </c>
       <c r="D212" s="17" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="E212" s="17" t="s">
         <v>49</v>
@@ -18425,10 +18422,10 @@
         <v>141</v>
       </c>
       <c r="G212" s="17" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H212" s="17" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="I212" s="17" t="s">
         <v>51</v>
@@ -18729,7 +18726,7 @@
         <v>400</v>
       </c>
       <c r="D217" s="17" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="E217" s="17" t="s">
         <v>49</v>
@@ -18738,10 +18735,10 @@
         <v>102</v>
       </c>
       <c r="G217" s="17" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="H217" s="17" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="I217" s="17" t="s">
         <v>84</v>
@@ -18792,7 +18789,7 @@
         <v>400</v>
       </c>
       <c r="D218" s="17" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="E218" s="17" t="s">
         <v>49</v>
@@ -18801,10 +18798,10 @@
         <v>102</v>
       </c>
       <c r="G218" s="17" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="H218" s="17" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="I218" s="17" t="s">
         <v>84</v>
@@ -18857,7 +18854,7 @@
         <v>400</v>
       </c>
       <c r="D219" s="17" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="E219" s="17" t="s">
         <v>49</v>
@@ -18866,10 +18863,10 @@
         <v>77</v>
       </c>
       <c r="G219" s="17" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="H219" s="17" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="I219" s="17" t="s">
         <v>84</v>
@@ -18922,7 +18919,7 @@
         <v>400</v>
       </c>
       <c r="D220" s="17" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="E220" s="17" t="s">
         <v>49</v>
@@ -18931,10 +18928,10 @@
         <v>102</v>
       </c>
       <c r="G220" s="17" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="H220" s="17" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="I220" s="17" t="s">
         <v>84</v>
@@ -18987,7 +18984,7 @@
         <v>400</v>
       </c>
       <c r="D221" s="17" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="E221" s="17" t="s">
         <v>49</v>
@@ -18996,10 +18993,10 @@
         <v>102</v>
       </c>
       <c r="G221" s="17" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="H221" s="17" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="I221" s="17" t="s">
         <v>84</v>
@@ -19310,7 +19307,7 @@
         <v>410</v>
       </c>
       <c r="D226" s="17" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="E226" s="17" t="s">
         <v>49</v>
@@ -19319,10 +19316,10 @@
         <v>29</v>
       </c>
       <c r="G226" s="17" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="H226" s="17" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="I226" s="4" t="s">
         <v>31</v>
@@ -19375,7 +19372,7 @@
         <v>410</v>
       </c>
       <c r="D227" s="17" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="E227" s="17" t="s">
         <v>49</v>
@@ -19384,10 +19381,10 @@
         <v>96</v>
       </c>
       <c r="G227" s="17" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="H227" s="17" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="I227" s="4" t="s">
         <v>31</v>
@@ -19440,7 +19437,7 @@
         <v>410</v>
       </c>
       <c r="D228" s="17" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="E228" s="17" t="s">
         <v>49</v>
@@ -19449,10 +19446,10 @@
         <v>96</v>
       </c>
       <c r="G228" s="17" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="H228" s="17" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="I228" s="4" t="s">
         <v>31</v>
@@ -19505,7 +19502,7 @@
         <v>410</v>
       </c>
       <c r="D229" s="17" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="E229" s="17" t="s">
         <v>49</v>
@@ -19514,10 +19511,10 @@
         <v>96</v>
       </c>
       <c r="G229" s="17" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="H229" s="17" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="I229" s="4" t="s">
         <v>31</v>
@@ -20155,7 +20152,7 @@
         <v>437</v>
       </c>
       <c r="D239" s="17" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="E239" s="17" t="s">
         <v>49</v>
@@ -20164,10 +20161,10 @@
         <v>282</v>
       </c>
       <c r="G239" s="17" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="H239" s="17" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="I239" s="17" t="s">
         <v>84</v>
@@ -20220,19 +20217,19 @@
         <v>437</v>
       </c>
       <c r="D240" s="17" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="E240" s="17" t="s">
         <v>28</v>
       </c>
       <c r="F240" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G240" s="17" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="H240" s="17" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="I240" s="17" t="s">
         <v>84</v>
@@ -20289,7 +20286,7 @@
         <v>28</v>
       </c>
       <c r="F241" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G241" s="4" t="s">
         <v>448</v>
@@ -20354,7 +20351,7 @@
         <v>28</v>
       </c>
       <c r="F242" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G242" s="4" t="s">
         <v>448</v>
@@ -20549,7 +20546,7 @@
         <v>28</v>
       </c>
       <c r="F245" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G245" s="4" t="s">
         <v>70</v>
@@ -20738,19 +20735,19 @@
         <v>445</v>
       </c>
       <c r="D248" s="17" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="E248" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F248" s="17" t="s">
-        <v>991</v>
+        <v>171</v>
       </c>
       <c r="G248" s="17" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="H248" s="17" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="I248" s="4" t="s">
         <v>31</v>
@@ -20793,7 +20790,7 @@
         <v>445</v>
       </c>
       <c r="D249" s="17" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="E249" s="17" t="s">
         <v>49</v>
@@ -20802,10 +20799,10 @@
         <v>29</v>
       </c>
       <c r="G249" s="4" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="H249" s="4" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="I249" s="17" t="s">
         <v>84</v>
@@ -20846,13 +20843,13 @@
         <v>445</v>
       </c>
       <c r="D250" s="17" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="E250" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F250" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G250" s="4" t="s">
         <v>448</v>
@@ -20905,7 +20902,7 @@
         <v>49</v>
       </c>
       <c r="F251" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G251" s="4" t="s">
         <v>70</v>
@@ -21165,7 +21162,7 @@
         <v>49</v>
       </c>
       <c r="F255" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G255" s="4" t="s">
         <v>487</v>
@@ -21224,7 +21221,7 @@
         <v>473</v>
       </c>
       <c r="D256" s="17" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="E256" s="17" t="s">
         <v>49</v>
@@ -21233,10 +21230,10 @@
         <v>110</v>
       </c>
       <c r="G256" s="17" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="H256" s="17" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="I256" s="17" t="s">
         <v>84</v>
@@ -21289,19 +21286,19 @@
         <v>473</v>
       </c>
       <c r="D257" s="17" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="E257" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F257" s="17" t="s">
-        <v>991</v>
+        <v>171</v>
       </c>
       <c r="G257" s="17" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="H257" s="17" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="I257" s="4" t="s">
         <v>31</v>
@@ -21354,7 +21351,7 @@
         <v>473</v>
       </c>
       <c r="D258" s="17" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="E258" s="17" t="s">
         <v>49</v>
@@ -21363,10 +21360,10 @@
         <v>110</v>
       </c>
       <c r="G258" s="17" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="H258" s="17" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="I258" s="4" t="s">
         <v>31</v>
@@ -21375,7 +21372,7 @@
         <v>62</v>
       </c>
       <c r="K258" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L258" s="13" t="s">
         <v>794</v>
@@ -21407,7 +21404,7 @@
         <v>473</v>
       </c>
       <c r="D259" s="17" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="E259" s="17" t="s">
         <v>49</v>
@@ -21416,10 +21413,10 @@
         <v>102</v>
       </c>
       <c r="G259" s="17" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="H259" s="17" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="I259" s="4" t="s">
         <v>31</v>
@@ -21608,7 +21605,7 @@
         <v>49</v>
       </c>
       <c r="F262" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G262" s="4" t="s">
         <v>70</v>
@@ -21735,7 +21732,7 @@
       <c r="E264" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F264" s="4" t="s">
+      <c r="F264" s="17" t="s">
         <v>171</v>
       </c>
       <c r="G264" s="4" t="s">
@@ -21793,7 +21790,7 @@
         <v>488</v>
       </c>
       <c r="D265" s="17" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="E265" s="17" t="s">
         <v>49</v>
@@ -21802,10 +21799,10 @@
         <v>147</v>
       </c>
       <c r="G265" s="17" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="H265" s="17" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="I265" s="4" t="s">
         <v>31</v>
@@ -21858,7 +21855,7 @@
         <v>488</v>
       </c>
       <c r="D266" s="17" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="E266" s="17" t="s">
         <v>49</v>
@@ -21867,10 +21864,10 @@
         <v>110</v>
       </c>
       <c r="G266" s="17" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="H266" s="17" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="I266" s="17" t="s">
         <v>84</v>
@@ -21923,7 +21920,7 @@
         <v>488</v>
       </c>
       <c r="D267" s="17" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="E267" s="17" t="s">
         <v>49</v>
@@ -21932,10 +21929,10 @@
         <v>147</v>
       </c>
       <c r="G267" s="17" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="H267" s="17" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="I267" s="17" t="s">
         <v>84</v>
@@ -21988,7 +21985,7 @@
         <v>488</v>
       </c>
       <c r="D268" s="17" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="E268" s="17" t="s">
         <v>28</v>
@@ -21997,10 +21994,10 @@
         <v>147</v>
       </c>
       <c r="G268" s="17" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="H268" s="17" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="I268" s="4" t="s">
         <v>31</v>
@@ -22053,19 +22050,19 @@
         <v>488</v>
       </c>
       <c r="D269" s="17" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="E269" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F269" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G269" s="17" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="H269" s="17" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="I269" s="4" t="s">
         <v>31</v>
@@ -22246,7 +22243,7 @@
         <v>500</v>
       </c>
       <c r="D272" s="17" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="E272" s="17" t="s">
         <v>49</v>
@@ -22255,10 +22252,10 @@
         <v>77</v>
       </c>
       <c r="G272" s="17" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="H272" s="17" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="I272" s="4" t="s">
         <v>31</v>
@@ -22311,7 +22308,7 @@
         <v>500</v>
       </c>
       <c r="D273" s="17" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="E273" s="17" t="s">
         <v>49</v>
@@ -22320,10 +22317,10 @@
         <v>503</v>
       </c>
       <c r="G273" s="17" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="H273" s="17" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="I273" s="4" t="s">
         <v>31</v>
@@ -22381,7 +22378,7 @@
       <c r="E274" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F274" s="4" t="s">
+      <c r="F274" s="17" t="s">
         <v>511</v>
       </c>
       <c r="G274" s="4" t="s">
@@ -22509,7 +22506,7 @@
       <c r="E276" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F276" s="4" t="s">
+      <c r="F276" s="17" t="s">
         <v>511</v>
       </c>
       <c r="G276" s="4" t="s">
@@ -22570,7 +22567,7 @@
       <c r="E277" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F277" s="4" t="s">
+      <c r="F277" s="17" t="s">
         <v>511</v>
       </c>
       <c r="G277" s="4" t="s">
@@ -22628,7 +22625,7 @@
         <v>509</v>
       </c>
       <c r="D278" s="17" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="E278" s="17" t="s">
         <v>49</v>
@@ -22637,10 +22634,10 @@
         <v>511</v>
       </c>
       <c r="G278" s="17" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="H278" s="17" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="I278" s="4" t="s">
         <v>31</v>
@@ -22693,7 +22690,7 @@
         <v>509</v>
       </c>
       <c r="D279" s="17" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="E279" s="17" t="s">
         <v>49</v>
@@ -22702,10 +22699,10 @@
         <v>511</v>
       </c>
       <c r="G279" s="17" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="H279" s="17" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I279" s="17" t="s">
         <v>84</v>
@@ -22714,7 +22711,7 @@
         <v>794</v>
       </c>
       <c r="K279" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L279" s="13" t="s">
         <v>794</v>
@@ -22758,7 +22755,7 @@
         <v>509</v>
       </c>
       <c r="D280" s="17" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="E280" s="17" t="s">
         <v>49</v>
@@ -22767,10 +22764,10 @@
         <v>511</v>
       </c>
       <c r="G280" s="17" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="H280" s="17" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="I280" s="17" t="s">
         <v>84</v>
@@ -22823,19 +22820,19 @@
         <v>509</v>
       </c>
       <c r="D281" s="17" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="E281" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F281" s="17" t="s">
-        <v>991</v>
+        <v>171</v>
       </c>
       <c r="G281" s="17" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="H281" s="17" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="I281" s="17" t="s">
         <v>84</v>
@@ -22888,7 +22885,7 @@
         <v>509</v>
       </c>
       <c r="D282" s="17" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="E282" s="17" t="s">
         <v>49</v>
@@ -22897,10 +22894,10 @@
         <v>77</v>
       </c>
       <c r="G282" s="17" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="H282" s="17" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="I282" s="17" t="s">
         <v>84</v>
@@ -22958,7 +22955,7 @@
       <c r="E283" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F283" s="4" t="s">
+      <c r="F283" s="17" t="s">
         <v>319</v>
       </c>
       <c r="G283" s="4" t="s">
@@ -23402,7 +23399,7 @@
         <v>519</v>
       </c>
       <c r="D290" s="17" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="E290" s="17" t="s">
         <v>49</v>
@@ -23411,10 +23408,10 @@
         <v>147</v>
       </c>
       <c r="G290" s="17" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="H290" s="17" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="I290" s="4" t="s">
         <v>31</v>
@@ -23467,7 +23464,7 @@
         <v>519</v>
       </c>
       <c r="D291" s="17" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="E291" s="17" t="s">
         <v>49</v>
@@ -23479,7 +23476,7 @@
         <v>362</v>
       </c>
       <c r="H291" s="17" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="I291" s="4" t="s">
         <v>31</v>
@@ -23512,7 +23509,7 @@
         <v>46</v>
       </c>
       <c r="S291" s="17" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="T291" s="17">
         <v>4</v>
@@ -23532,7 +23529,7 @@
         <v>519</v>
       </c>
       <c r="D292" s="17" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="E292" s="17" t="s">
         <v>28</v>
@@ -23541,10 +23538,10 @@
         <v>96</v>
       </c>
       <c r="G292" s="17" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="H292" s="17" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="I292" s="17" t="s">
         <v>84</v>
@@ -23597,7 +23594,7 @@
         <v>519</v>
       </c>
       <c r="D293" s="17" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="E293" s="17" t="s">
         <v>49</v>
@@ -23606,10 +23603,10 @@
         <v>253</v>
       </c>
       <c r="G293" s="17" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="H293" s="17" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="I293" s="17" t="s">
         <v>84</v>
@@ -23730,7 +23727,7 @@
       <c r="E295" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F295" s="4" t="s">
+      <c r="F295" s="17" t="s">
         <v>511</v>
       </c>
       <c r="G295" s="4" t="s">
@@ -23855,19 +23852,19 @@
         <v>540</v>
       </c>
       <c r="D297" s="17" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="E297" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F297" s="17" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="G297" s="17" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="H297" s="17" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="I297" s="4" t="s">
         <v>31</v>
@@ -23920,7 +23917,7 @@
         <v>540</v>
       </c>
       <c r="D298" s="17" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="E298" s="17" t="s">
         <v>49</v>
@@ -23929,10 +23926,10 @@
         <v>82</v>
       </c>
       <c r="G298" s="17" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="H298" s="17" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="I298" s="4" t="s">
         <v>31</v>
@@ -23985,10 +23982,10 @@
         <v>540</v>
       </c>
       <c r="D299" s="17" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="E299" s="17" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="F299" s="17" t="s">
         <v>40</v>
@@ -24056,7 +24053,7 @@
         <v>49</v>
       </c>
       <c r="F300" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G300" s="4" t="s">
         <v>70</v>
@@ -24112,7 +24109,7 @@
       <c r="E301" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F301" s="4" t="s">
+      <c r="F301" s="17" t="s">
         <v>171</v>
       </c>
       <c r="G301" s="4" t="s">
@@ -24164,7 +24161,7 @@
         <v>551</v>
       </c>
       <c r="D302" s="17" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="E302" s="17" t="s">
         <v>49</v>
@@ -24173,10 +24170,10 @@
         <v>77</v>
       </c>
       <c r="G302" s="17" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H302" s="17" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="I302" s="4" t="s">
         <v>31</v>
@@ -24229,12 +24226,12 @@
         <v>551</v>
       </c>
       <c r="D303" s="17" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="E303" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="F303" s="4" t="s">
+      <c r="F303" s="17" t="s">
         <v>171</v>
       </c>
       <c r="G303" s="4" t="s">
@@ -24294,19 +24291,19 @@
         <v>551</v>
       </c>
       <c r="D304" s="17" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="E304" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F304" s="17" t="s">
-        <v>991</v>
+        <v>171</v>
       </c>
       <c r="G304" s="18" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="H304" s="18" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="I304" s="17" t="s">
         <v>84</v>
@@ -24429,7 +24426,7 @@
       <c r="E306" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F306" s="4" t="s">
+      <c r="F306" s="17" t="s">
         <v>319</v>
       </c>
       <c r="G306" s="4" t="s">
@@ -24624,7 +24621,7 @@
       <c r="E309" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F309" s="4" t="s">
+      <c r="F309" s="17" t="s">
         <v>319</v>
       </c>
       <c r="G309" s="4" t="s">
@@ -24689,7 +24686,7 @@
       <c r="E310" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F310" s="4" t="s">
+      <c r="F310" s="17" t="s">
         <v>319</v>
       </c>
       <c r="G310" s="4" t="s">
@@ -24754,8 +24751,8 @@
       <c r="E311" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F311" s="4" t="s">
-        <v>283</v>
+      <c r="F311" s="17" t="s">
+        <v>282</v>
       </c>
       <c r="G311" s="4" t="s">
         <v>574</v>
@@ -24814,7 +24811,7 @@
         <v>558</v>
       </c>
       <c r="D312" s="17" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="E312" s="17" t="s">
         <v>49</v>
@@ -24823,10 +24820,10 @@
         <v>319</v>
       </c>
       <c r="G312" s="17" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="H312" s="17" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="I312" s="17" t="s">
         <v>84</v>
@@ -24835,7 +24832,7 @@
         <v>247</v>
       </c>
       <c r="K312" s="17" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="L312" s="13" t="s">
         <v>247</v>
@@ -24879,7 +24876,7 @@
         <v>558</v>
       </c>
       <c r="D313" s="17" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="E313" s="17" t="s">
         <v>49</v>
@@ -24888,10 +24885,10 @@
         <v>77</v>
       </c>
       <c r="G313" s="17" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="H313" s="17" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="I313" s="4" t="s">
         <v>31</v>
@@ -24944,7 +24941,7 @@
         <v>558</v>
       </c>
       <c r="D314" s="17" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="E314" s="17" t="s">
         <v>49</v>
@@ -24953,10 +24950,10 @@
         <v>319</v>
       </c>
       <c r="G314" s="17" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="H314" s="17" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="I314" s="17" t="s">
         <v>84</v>
@@ -25009,19 +25006,19 @@
         <v>558</v>
       </c>
       <c r="D315" s="17" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="E315" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F315" s="17" t="s">
-        <v>85</v>
+        <v>319</v>
       </c>
       <c r="G315" s="17" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="H315" s="17" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I315" s="4" t="s">
         <v>31</v>
@@ -25074,7 +25071,7 @@
         <v>558</v>
       </c>
       <c r="D316" s="17" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="E316" s="17" t="s">
         <v>49</v>
@@ -25083,10 +25080,10 @@
         <v>96</v>
       </c>
       <c r="G316" s="17" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="H316" s="17" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="I316" s="4" t="s">
         <v>31</v>
@@ -25095,7 +25092,7 @@
         <v>794</v>
       </c>
       <c r="K316" s="17" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="L316" s="13" t="s">
         <v>794</v>
@@ -25334,7 +25331,7 @@
         <v>575</v>
       </c>
       <c r="D320" s="17" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="E320" s="17" t="s">
         <v>28</v>
@@ -25343,10 +25340,10 @@
         <v>77</v>
       </c>
       <c r="G320" s="17" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H320" s="17" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="I320" s="4" t="s">
         <v>31</v>
@@ -25399,7 +25396,7 @@
         <v>575</v>
       </c>
       <c r="D321" s="17" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="E321" s="17" t="s">
         <v>49</v>
@@ -25408,10 +25405,10 @@
         <v>77</v>
       </c>
       <c r="G321" s="17" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="H321" s="17" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="I321" s="4" t="s">
         <v>31</v>
@@ -25464,7 +25461,7 @@
         <v>575</v>
       </c>
       <c r="D322" s="17" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="E322" s="17" t="s">
         <v>49</v>
@@ -25473,10 +25470,10 @@
         <v>77</v>
       </c>
       <c r="G322" s="17" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="H322" s="17" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="I322" s="4" t="s">
         <v>31</v>
@@ -25598,7 +25595,7 @@
         <v>49</v>
       </c>
       <c r="F324" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G324" s="4" t="s">
         <v>70</v>
@@ -25661,7 +25658,7 @@
         <v>49</v>
       </c>
       <c r="F325" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G325" s="4" t="s">
         <v>70</v>
@@ -25726,7 +25723,7 @@
         <v>49</v>
       </c>
       <c r="F326" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G326" s="4" t="s">
         <v>70</v>
@@ -25791,7 +25788,7 @@
         <v>28</v>
       </c>
       <c r="F327" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G327" s="4" t="s">
         <v>70</v>
@@ -25856,7 +25853,7 @@
         <v>49</v>
       </c>
       <c r="F328" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G328" s="4" t="s">
         <v>597</v>
@@ -25986,7 +25983,7 @@
         <v>49</v>
       </c>
       <c r="F330" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G330" s="4" t="s">
         <v>602</v>
@@ -26051,7 +26048,7 @@
         <v>49</v>
       </c>
       <c r="F331" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G331" s="4" t="s">
         <v>448</v>
@@ -26116,7 +26113,7 @@
         <v>49</v>
       </c>
       <c r="F332" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G332" s="4" t="s">
         <v>70</v>
@@ -26173,19 +26170,19 @@
         <v>583</v>
       </c>
       <c r="D333" s="17" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="E333" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F333" s="17" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G333" s="17" t="s">
         <v>929</v>
       </c>
-      <c r="G333" s="17" t="s">
-        <v>930</v>
-      </c>
       <c r="H333" s="17" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I333" s="4" t="s">
         <v>31</v>
@@ -26238,19 +26235,19 @@
         <v>583</v>
       </c>
       <c r="D334" s="17" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="E334" s="17" t="s">
         <v>28</v>
       </c>
       <c r="F334" s="17" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G334" s="17" t="s">
         <v>929</v>
       </c>
-      <c r="G334" s="17" t="s">
-        <v>930</v>
-      </c>
       <c r="H334" s="17" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I334" s="4" t="s">
         <v>31</v>
@@ -26301,19 +26298,19 @@
         <v>583</v>
       </c>
       <c r="D335" s="17" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="E335" s="17" t="s">
         <v>28</v>
       </c>
       <c r="F335" s="17" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G335" s="17" t="s">
         <v>929</v>
       </c>
-      <c r="G335" s="17" t="s">
-        <v>930</v>
-      </c>
       <c r="H335" s="17" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I335" s="4" t="s">
         <v>31</v>
@@ -26322,7 +26319,7 @@
         <v>915</v>
       </c>
       <c r="K335" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L335" s="13" t="s">
         <v>915</v>
@@ -26331,7 +26328,7 @@
         <v>43</v>
       </c>
       <c r="N335" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="O335" s="4" t="s">
         <v>38</v>
@@ -26366,19 +26363,19 @@
         <v>583</v>
       </c>
       <c r="D336" s="17" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="E336" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F336" s="17" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G336" s="17" t="s">
         <v>929</v>
       </c>
-      <c r="G336" s="17" t="s">
-        <v>930</v>
-      </c>
       <c r="H336" s="17" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I336" s="4" t="s">
         <v>31</v>
@@ -26431,19 +26428,19 @@
         <v>583</v>
       </c>
       <c r="D337" s="17" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="E337" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F337" s="17" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G337" s="17" t="s">
         <v>929</v>
       </c>
-      <c r="G337" s="17" t="s">
-        <v>930</v>
-      </c>
       <c r="H337" s="17" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I337" s="4" t="s">
         <v>31</v>
@@ -26496,19 +26493,19 @@
         <v>583</v>
       </c>
       <c r="D338" s="17" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="E338" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F338" s="17" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G338" s="17" t="s">
         <v>929</v>
       </c>
-      <c r="G338" s="17" t="s">
-        <v>930</v>
-      </c>
       <c r="H338" s="17" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I338" s="4" t="s">
         <v>31</v>
@@ -26517,7 +26514,7 @@
         <v>915</v>
       </c>
       <c r="K338" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L338" s="13" t="s">
         <v>915</v>
@@ -26526,7 +26523,7 @@
         <v>43</v>
       </c>
       <c r="N338" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="O338" s="4" t="s">
         <v>38</v>
@@ -26561,19 +26558,19 @@
         <v>583</v>
       </c>
       <c r="D339" s="17" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="E339" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F339" s="17" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G339" s="17" t="s">
         <v>929</v>
       </c>
-      <c r="G339" s="17" t="s">
-        <v>930</v>
-      </c>
       <c r="H339" s="17" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I339" s="4" t="s">
         <v>31</v>
@@ -26582,7 +26579,7 @@
         <v>915</v>
       </c>
       <c r="K339" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L339" s="13" t="s">
         <v>915</v>
@@ -26591,7 +26588,7 @@
         <v>44</v>
       </c>
       <c r="N339" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="O339" s="4" t="s">
         <v>38</v>
@@ -26623,10 +26620,10 @@
         <v>923</v>
       </c>
       <c r="C340" s="17" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D340" s="17" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="E340" s="17" t="s">
         <v>49</v>
@@ -26635,10 +26632,10 @@
         <v>65</v>
       </c>
       <c r="G340" s="17" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="H340" s="17" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="I340" s="4" t="s">
         <v>31</v>
@@ -26688,10 +26685,10 @@
         <v>923</v>
       </c>
       <c r="C341" s="17" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D341" s="17" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="E341" s="17" t="s">
         <v>49</v>
@@ -26700,10 +26697,10 @@
         <v>65</v>
       </c>
       <c r="G341" s="17" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="H341" s="17" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="I341" s="4" t="s">
         <v>31</v>
@@ -26712,7 +26709,7 @@
         <v>911</v>
       </c>
       <c r="K341" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L341" s="13" t="s">
         <v>911</v>
@@ -26753,10 +26750,10 @@
         <v>923</v>
       </c>
       <c r="C342" s="17" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D342" s="17" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="E342" s="17" t="s">
         <v>28</v>
@@ -26765,10 +26762,10 @@
         <v>65</v>
       </c>
       <c r="G342" s="17" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="H342" s="17" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="I342" s="4" t="s">
         <v>31</v>
@@ -26777,7 +26774,7 @@
         <v>794</v>
       </c>
       <c r="K342" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L342" s="13" t="s">
         <v>794</v>
@@ -26818,10 +26815,10 @@
         <v>923</v>
       </c>
       <c r="C343" s="17" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D343" s="17" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="E343" s="17" t="s">
         <v>49</v>
@@ -26830,10 +26827,10 @@
         <v>65</v>
       </c>
       <c r="G343" s="17" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="H343" s="17" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="I343" s="4" t="s">
         <v>31</v>
@@ -26842,7 +26839,7 @@
         <v>794</v>
       </c>
       <c r="K343" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L343" s="13" t="s">
         <v>794</v>
@@ -26883,7 +26880,7 @@
         <v>908</v>
       </c>
       <c r="C344" s="17" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D344" s="3" t="s">
         <v>607</v>
@@ -26946,7 +26943,7 @@
         <v>908</v>
       </c>
       <c r="C345" s="17" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D345" s="3" t="s">
         <v>611</v>
@@ -27009,7 +27006,7 @@
         <v>908</v>
       </c>
       <c r="C346" s="17" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D346" s="3" t="s">
         <v>613</v>
@@ -27072,7 +27069,7 @@
         <v>908</v>
       </c>
       <c r="C347" s="17" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D347" s="3" t="s">
         <v>617</v>
@@ -27135,7 +27132,7 @@
         <v>908</v>
       </c>
       <c r="C348" s="17" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D348" s="3" t="s">
         <v>619</v>
@@ -27198,7 +27195,7 @@
         <v>908</v>
       </c>
       <c r="C349" s="17" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D349" s="3" t="s">
         <v>622</v>
@@ -27261,7 +27258,7 @@
         <v>908</v>
       </c>
       <c r="C350" s="17" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D350" s="3" t="s">
         <v>624</v>
@@ -27324,7 +27321,7 @@
         <v>908</v>
       </c>
       <c r="C351" s="17" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D351" s="3" t="s">
         <v>627</v>
@@ -27585,7 +27582,7 @@
         <v>628</v>
       </c>
       <c r="D355" s="17" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="E355" s="17" t="s">
         <v>49</v>
@@ -27594,10 +27591,10 @@
         <v>65</v>
       </c>
       <c r="G355" s="17" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="H355" s="17" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="I355" s="4" t="s">
         <v>31</v>
@@ -27650,7 +27647,7 @@
         <v>628</v>
       </c>
       <c r="D356" s="17" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="E356" s="17" t="s">
         <v>49</v>
@@ -27715,7 +27712,7 @@
         <v>628</v>
       </c>
       <c r="D357" s="17" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="E357" s="17" t="s">
         <v>49</v>
@@ -27780,7 +27777,7 @@
         <v>628</v>
       </c>
       <c r="D358" s="17" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="E358" s="17" t="s">
         <v>49</v>
@@ -27789,10 +27786,10 @@
         <v>65</v>
       </c>
       <c r="G358" s="17" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="H358" s="17" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="I358" s="17" t="s">
         <v>84</v>
@@ -28235,7 +28232,7 @@
         <v>639</v>
       </c>
       <c r="D365" s="17" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="E365" s="17" t="s">
         <v>28</v>
@@ -28300,7 +28297,7 @@
         <v>639</v>
       </c>
       <c r="D366" s="17" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="E366" s="17" t="s">
         <v>28</v>
@@ -28309,10 +28306,10 @@
         <v>102</v>
       </c>
       <c r="G366" s="17" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="H366" s="17" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="I366" s="4" t="s">
         <v>31</v>
@@ -28365,7 +28362,7 @@
         <v>639</v>
       </c>
       <c r="D367" s="17" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="E367" s="17" t="s">
         <v>49</v>
@@ -28374,10 +28371,10 @@
         <v>102</v>
       </c>
       <c r="G367" s="17" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="H367" s="17" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="I367" s="4" t="s">
         <v>31</v>
@@ -28430,7 +28427,7 @@
         <v>639</v>
       </c>
       <c r="D368" s="17" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="E368" s="17" t="s">
         <v>49</v>
@@ -28495,7 +28492,7 @@
         <v>639</v>
       </c>
       <c r="D369" s="17" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="E369" s="17" t="s">
         <v>49</v>
@@ -28504,10 +28501,10 @@
         <v>102</v>
       </c>
       <c r="G369" s="17" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="H369" s="17" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="I369" s="4" t="s">
         <v>31</v>
@@ -28560,7 +28557,7 @@
         <v>639</v>
       </c>
       <c r="D370" s="17" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="E370" s="17" t="s">
         <v>49</v>
@@ -28569,10 +28566,10 @@
         <v>102</v>
       </c>
       <c r="G370" s="17" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="H370" s="17" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="I370" s="4" t="s">
         <v>31</v>
@@ -28877,7 +28874,7 @@
         <v>655</v>
       </c>
       <c r="D375" s="17" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="E375" s="17" t="s">
         <v>28</v>
@@ -28886,10 +28883,10 @@
         <v>96</v>
       </c>
       <c r="G375" s="17" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="H375" s="17" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="I375" s="4" t="s">
         <v>31</v>
@@ -28942,7 +28939,7 @@
         <v>655</v>
       </c>
       <c r="D376" s="17" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="E376" s="17" t="s">
         <v>49</v>
@@ -28951,10 +28948,10 @@
         <v>96</v>
       </c>
       <c r="G376" s="17" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H376" s="17" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="I376" s="4" t="s">
         <v>31</v>
@@ -29007,7 +29004,7 @@
         <v>655</v>
       </c>
       <c r="D377" s="17" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="E377" s="17" t="s">
         <v>49</v>
@@ -29016,10 +29013,10 @@
         <v>55</v>
       </c>
       <c r="G377" s="17" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H377" s="17" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="I377" s="17" t="s">
         <v>51</v>
@@ -29544,7 +29541,7 @@
         <v>664</v>
       </c>
       <c r="D386" s="17" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="E386" s="17" t="s">
         <v>49</v>
@@ -29553,10 +29550,10 @@
         <v>65</v>
       </c>
       <c r="G386" s="17" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="H386" s="17" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="I386" s="4" t="s">
         <v>31</v>
@@ -29609,7 +29606,7 @@
         <v>664</v>
       </c>
       <c r="D387" s="17" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="E387" s="17" t="s">
         <v>28</v>
@@ -29618,10 +29615,10 @@
         <v>65</v>
       </c>
       <c r="G387" s="17" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="H387" s="17" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="I387" s="17" t="s">
         <v>84</v>
@@ -29674,7 +29671,7 @@
         <v>664</v>
       </c>
       <c r="D388" s="17" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="E388" s="17" t="s">
         <v>49</v>
@@ -29683,10 +29680,10 @@
         <v>65</v>
       </c>
       <c r="G388" s="17" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="H388" s="17" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="I388" s="4" t="s">
         <v>31</v>
@@ -29739,7 +29736,7 @@
         <v>664</v>
       </c>
       <c r="D389" s="17" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="E389" s="17" t="s">
         <v>49</v>
@@ -29748,10 +29745,10 @@
         <v>65</v>
       </c>
       <c r="G389" s="17" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="H389" s="17" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="I389" s="4" t="s">
         <v>31</v>
@@ -29804,7 +29801,7 @@
         <v>664</v>
       </c>
       <c r="D390" s="17" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="E390" s="4" t="s">
         <v>480</v>
@@ -29813,10 +29810,10 @@
         <v>65</v>
       </c>
       <c r="G390" s="17" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="H390" s="17" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="I390" s="4" t="s">
         <v>31</v>
@@ -29869,7 +29866,7 @@
         <v>664</v>
       </c>
       <c r="D391" s="17" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="E391" s="17" t="s">
         <v>49</v>
@@ -29878,10 +29875,10 @@
         <v>65</v>
       </c>
       <c r="G391" s="17" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="H391" s="17" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="I391" s="4" t="s">
         <v>31</v>
@@ -29890,7 +29887,7 @@
         <v>444</v>
       </c>
       <c r="K391" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L391" s="13" t="s">
         <v>444</v>
@@ -29934,7 +29931,7 @@
         <v>679</v>
       </c>
       <c r="D392" s="17" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="E392" s="17" t="s">
         <v>49</v>
@@ -29943,10 +29940,10 @@
         <v>29</v>
       </c>
       <c r="G392" s="17" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="H392" s="17" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="I392" s="17" t="s">
         <v>84</v>
@@ -29999,7 +29996,7 @@
         <v>679</v>
       </c>
       <c r="D393" s="17" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="E393" s="17" t="s">
         <v>49</v>
@@ -30008,10 +30005,10 @@
         <v>110</v>
       </c>
       <c r="G393" s="17" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="H393" s="17" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="I393" s="17" t="s">
         <v>84</v>
@@ -30064,7 +30061,7 @@
         <v>679</v>
       </c>
       <c r="D394" s="17" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="E394" s="17" t="s">
         <v>49</v>
@@ -30073,10 +30070,10 @@
         <v>77</v>
       </c>
       <c r="G394" s="17" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="H394" s="17" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="I394" s="4" t="s">
         <v>31</v>
@@ -30129,7 +30126,7 @@
         <v>679</v>
       </c>
       <c r="D395" s="17" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="E395" s="17" t="s">
         <v>49</v>
@@ -30138,10 +30135,10 @@
         <v>77</v>
       </c>
       <c r="G395" s="17" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H395" s="17" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="I395" s="4" t="s">
         <v>31</v>
@@ -30194,7 +30191,7 @@
         <v>679</v>
       </c>
       <c r="D396" s="17" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="E396" s="17" t="s">
         <v>49</v>
@@ -30203,10 +30200,10 @@
         <v>77</v>
       </c>
       <c r="G396" s="17" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H396" s="17" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="I396" s="4" t="s">
         <v>31</v>
@@ -30215,7 +30212,7 @@
         <v>911</v>
       </c>
       <c r="K396" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L396" s="13"/>
       <c r="M396" s="17" t="s">
@@ -30257,7 +30254,7 @@
         <v>679</v>
       </c>
       <c r="D397" s="17" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="E397" s="17" t="s">
         <v>49</v>
@@ -30266,10 +30263,10 @@
         <v>77</v>
       </c>
       <c r="G397" s="17" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="H397" s="17" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="I397" s="17" t="s">
         <v>84</v>
@@ -30278,7 +30275,7 @@
         <v>915</v>
       </c>
       <c r="K397" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L397" s="13" t="s">
         <v>915</v>
@@ -30322,7 +30319,7 @@
         <v>679</v>
       </c>
       <c r="D398" s="17" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="E398" s="17" t="s">
         <v>49</v>
@@ -30331,10 +30328,10 @@
         <v>40</v>
       </c>
       <c r="G398" s="17" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="H398" s="17" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="I398" s="4" t="s">
         <v>31</v>
@@ -30522,7 +30519,7 @@
       <c r="E401" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F401" s="4" t="s">
+      <c r="F401" s="17" t="s">
         <v>319</v>
       </c>
       <c r="G401" s="4" t="s">
@@ -30901,7 +30898,7 @@
         <v>422</v>
       </c>
       <c r="D407" s="17" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="E407" s="17" t="s">
         <v>49</v>
@@ -30910,10 +30907,10 @@
         <v>110</v>
       </c>
       <c r="G407" s="17" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="H407" s="17" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="I407" s="4" t="s">
         <v>31</v>
@@ -30964,7 +30961,7 @@
         <v>422</v>
       </c>
       <c r="D408" s="17" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="E408" s="17" t="s">
         <v>49</v>
@@ -30973,10 +30970,10 @@
         <v>110</v>
       </c>
       <c r="G408" s="17" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="H408" s="17" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="I408" s="4" t="s">
         <v>31</v>
@@ -31029,7 +31026,7 @@
         <v>422</v>
       </c>
       <c r="D409" s="17" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="E409" s="17" t="s">
         <v>49</v>
@@ -31038,10 +31035,10 @@
         <v>110</v>
       </c>
       <c r="G409" s="17" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="H409" s="17" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="I409" s="4" t="s">
         <v>31</v>
@@ -31092,7 +31089,7 @@
         <v>422</v>
       </c>
       <c r="D410" s="17" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="E410" s="17" t="s">
         <v>49</v>
@@ -31101,10 +31098,10 @@
         <v>29</v>
       </c>
       <c r="G410" s="17" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="H410" s="17" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="I410" s="17" t="s">
         <v>84</v>
@@ -31155,19 +31152,19 @@
         <v>422</v>
       </c>
       <c r="D411" s="17" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="E411" s="17" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="F411" s="17" t="s">
         <v>110</v>
       </c>
       <c r="G411" s="17" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="H411" s="17" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="I411" s="4" t="s">
         <v>31</v>
@@ -31208,7 +31205,7 @@
         <v>422</v>
       </c>
       <c r="D412" s="17" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="E412" s="17" t="s">
         <v>49</v>
@@ -31273,7 +31270,7 @@
         <v>422</v>
       </c>
       <c r="D413" s="17" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="E413" s="17" t="s">
         <v>49</v>
@@ -31282,7 +31279,7 @@
         <v>141</v>
       </c>
       <c r="G413" s="17" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="H413" s="4"/>
       <c r="I413" s="17" t="s">
@@ -31659,7 +31656,7 @@
         <v>699</v>
       </c>
       <c r="D419" s="17" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="E419" s="17" t="s">
         <v>49</v>
@@ -31668,10 +31665,10 @@
         <v>141</v>
       </c>
       <c r="G419" s="17" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="H419" s="17" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="I419" s="17" t="s">
         <v>84</v>
@@ -31724,7 +31721,7 @@
         <v>699</v>
       </c>
       <c r="D420" s="17" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="E420" s="17" t="s">
         <v>49</v>
@@ -31733,10 +31730,10 @@
         <v>77</v>
       </c>
       <c r="G420" s="17" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="H420" s="17" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="I420" s="4" t="s">
         <v>31</v>
@@ -31745,7 +31742,7 @@
         <v>444</v>
       </c>
       <c r="K420" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L420" s="13" t="s">
         <v>794</v>
@@ -31789,7 +31786,7 @@
         <v>699</v>
       </c>
       <c r="D421" s="17" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="E421" s="17" t="s">
         <v>49</v>
@@ -31798,10 +31795,10 @@
         <v>141</v>
       </c>
       <c r="G421" s="17" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="H421" s="17" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="I421" s="17" t="s">
         <v>84</v>
@@ -31854,7 +31851,7 @@
         <v>699</v>
       </c>
       <c r="D422" s="17" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="E422" s="17" t="s">
         <v>49</v>
@@ -31863,10 +31860,10 @@
         <v>141</v>
       </c>
       <c r="G422" s="17" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="H422" s="17" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="I422" s="17" t="s">
         <v>84</v>
@@ -31919,7 +31916,7 @@
         <v>714</v>
       </c>
       <c r="D423" s="17" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="E423" s="17" t="s">
         <v>49</v>
@@ -31928,10 +31925,10 @@
         <v>147</v>
       </c>
       <c r="G423" s="17" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="H423" s="17" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="I423" s="4" t="s">
         <v>31</v>
@@ -31984,7 +31981,7 @@
         <v>714</v>
       </c>
       <c r="D424" s="17" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E424" s="17" t="s">
         <v>49</v>
@@ -31993,10 +31990,10 @@
         <v>147</v>
       </c>
       <c r="G424" s="17" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="H424" s="17" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="I424" s="17" t="s">
         <v>84</v>
@@ -32176,7 +32173,7 @@
         <v>908</v>
       </c>
       <c r="C427" s="17" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="D427" s="3" t="s">
         <v>723</v>
@@ -32241,7 +32238,7 @@
         <v>908</v>
       </c>
       <c r="C428" s="17" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="D428" s="3" t="s">
         <v>725</v>
@@ -32306,7 +32303,7 @@
         <v>908</v>
       </c>
       <c r="C429" s="17" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="D429" s="3" t="s">
         <v>727</v>
@@ -32371,10 +32368,10 @@
         <v>923</v>
       </c>
       <c r="C430" s="17" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="D430" s="17" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="E430" s="17" t="s">
         <v>49</v>
@@ -32383,10 +32380,10 @@
         <v>77</v>
       </c>
       <c r="G430" s="17" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="H430" s="17" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="I430" s="4" t="s">
         <v>31</v>
@@ -32436,10 +32433,10 @@
         <v>923</v>
       </c>
       <c r="C431" s="17" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D431" s="17" t="s">
         <v>1293</v>
-      </c>
-      <c r="D431" s="17" t="s">
-        <v>1295</v>
       </c>
       <c r="E431" s="17" t="s">
         <v>49</v>
@@ -32448,10 +32445,10 @@
         <v>77</v>
       </c>
       <c r="G431" s="17" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="H431" s="17" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="I431" s="4" t="s">
         <v>31</v>
@@ -32501,10 +32498,10 @@
         <v>923</v>
       </c>
       <c r="C432" s="17" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="D432" s="17" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="E432" s="17" t="s">
         <v>49</v>
@@ -32513,10 +32510,10 @@
         <v>77</v>
       </c>
       <c r="G432" s="17" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="H432" s="17" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="I432" s="4" t="s">
         <v>31</v>
@@ -32699,7 +32696,7 @@
         <v>729</v>
       </c>
       <c r="D435" s="17" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="E435" s="17" t="s">
         <v>49</v>
@@ -32708,10 +32705,10 @@
         <v>77</v>
       </c>
       <c r="G435" s="17" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="H435" s="17" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="I435" s="4" t="s">
         <v>31</v>
@@ -32764,7 +32761,7 @@
         <v>729</v>
       </c>
       <c r="D436" s="17" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="E436" s="17" t="s">
         <v>28</v>
@@ -32773,10 +32770,10 @@
         <v>77</v>
       </c>
       <c r="G436" s="17" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H436" s="17" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="I436" s="17" t="s">
         <v>84</v>
@@ -32829,7 +32826,7 @@
         <v>736</v>
       </c>
       <c r="D437" s="17" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="E437" s="17" t="s">
         <v>49</v>
@@ -32894,7 +32891,7 @@
         <v>736</v>
       </c>
       <c r="D438" s="17" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="E438" s="17" t="s">
         <v>49</v>
@@ -32903,10 +32900,10 @@
         <v>147</v>
       </c>
       <c r="G438" s="17" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="H438" s="17" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="I438" s="17" t="s">
         <v>84</v>
@@ -32959,19 +32956,19 @@
         <v>736</v>
       </c>
       <c r="D439" s="17" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="E439" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F439" s="17" t="s">
-        <v>991</v>
+        <v>171</v>
       </c>
       <c r="G439" s="17" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="H439" s="17" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="I439" s="4" t="s">
         <v>31</v>
@@ -33024,7 +33021,7 @@
         <v>736</v>
       </c>
       <c r="D440" s="17" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="E440" s="17" t="s">
         <v>28</v>
@@ -33033,10 +33030,10 @@
         <v>82</v>
       </c>
       <c r="G440" s="17" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="H440" s="17" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="I440" s="4" t="s">
         <v>31</v>
@@ -33045,7 +33042,7 @@
         <v>247</v>
       </c>
       <c r="K440" s="17" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="L440" s="13" t="s">
         <v>247</v>
@@ -33089,7 +33086,7 @@
         <v>736</v>
       </c>
       <c r="D441" s="17" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="E441" s="17" t="s">
         <v>28</v>
@@ -33098,10 +33095,10 @@
         <v>82</v>
       </c>
       <c r="G441" s="17" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="H441" s="17" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="I441" s="4" t="s">
         <v>31</v>
@@ -33154,7 +33151,7 @@
         <v>736</v>
       </c>
       <c r="D442" s="17" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="E442" s="17" t="s">
         <v>49</v>
@@ -33163,10 +33160,10 @@
         <v>82</v>
       </c>
       <c r="G442" s="17" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="H442" s="17" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="I442" s="4" t="s">
         <v>31</v>
@@ -33175,7 +33172,7 @@
         <v>247</v>
       </c>
       <c r="K442" s="17" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="L442" s="13" t="s">
         <v>794</v>
@@ -33219,7 +33216,7 @@
         <v>736</v>
       </c>
       <c r="D443" s="17" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="E443" s="17" t="s">
         <v>49</v>
@@ -33284,7 +33281,7 @@
         <v>736</v>
       </c>
       <c r="D444" s="17" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="E444" s="17" t="s">
         <v>28</v>
@@ -33293,10 +33290,10 @@
         <v>102</v>
       </c>
       <c r="G444" s="4" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="H444" s="4" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="I444" s="4" t="s">
         <v>31</v>
@@ -33736,10 +33733,10 @@
         <v>923</v>
       </c>
       <c r="C451" s="17" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="D451" s="17" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="E451" s="17" t="s">
         <v>49</v>
@@ -33748,10 +33745,10 @@
         <v>309</v>
       </c>
       <c r="G451" s="17" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="H451" s="17" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="I451" s="4" t="s">
         <v>31</v>
@@ -33760,7 +33757,7 @@
         <v>247</v>
       </c>
       <c r="K451" s="17" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="L451" s="13" t="s">
         <v>247</v>
@@ -33801,10 +33798,10 @@
         <v>923</v>
       </c>
       <c r="C452" s="17" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="D452" s="17" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="E452" s="17" t="s">
         <v>49</v>
@@ -33813,10 +33810,10 @@
         <v>309</v>
       </c>
       <c r="G452" s="17" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="H452" s="17" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="I452" s="4" t="s">
         <v>31</v>
@@ -33866,10 +33863,10 @@
         <v>923</v>
       </c>
       <c r="C453" s="17" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="D453" s="17" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="E453" s="17" t="s">
         <v>49</v>
@@ -33878,10 +33875,10 @@
         <v>309</v>
       </c>
       <c r="G453" s="17" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="H453" s="17" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="I453" s="4" t="s">
         <v>31</v>
@@ -33929,10 +33926,10 @@
         <v>923</v>
       </c>
       <c r="C454" s="17" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="D454" s="17" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="E454" s="17" t="s">
         <v>49</v>
@@ -33941,10 +33938,10 @@
         <v>309</v>
       </c>
       <c r="G454" s="17" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="H454" s="17" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="I454" s="4" t="s">
         <v>31</v>
@@ -33953,7 +33950,7 @@
         <v>247</v>
       </c>
       <c r="K454" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L454" s="13" t="s">
         <v>247</v>
@@ -33994,10 +33991,10 @@
         <v>923</v>
       </c>
       <c r="C455" s="17" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="D455" s="17" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="E455" s="17" t="s">
         <v>49</v>
@@ -34006,16 +34003,16 @@
         <v>309</v>
       </c>
       <c r="G455" s="17" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="H455" s="17" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="I455" s="4" t="s">
         <v>31</v>
       </c>
       <c r="J455" s="13" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="K455" s="17" t="s">
         <v>927</v>
@@ -34059,7 +34056,7 @@
         <v>908</v>
       </c>
       <c r="C456" s="17" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="D456" s="3" t="s">
         <v>761</v>
@@ -34124,7 +34121,7 @@
         <v>908</v>
       </c>
       <c r="C457" s="17" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="D457" s="3" t="s">
         <v>765</v>
@@ -34192,7 +34189,7 @@
         <v>767</v>
       </c>
       <c r="D458" s="17" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E458" s="17" t="s">
         <v>49</v>
@@ -34201,10 +34198,10 @@
         <v>55</v>
       </c>
       <c r="G458" s="17" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="H458" s="17" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="I458" s="4" t="s">
         <v>31</v>
@@ -34257,7 +34254,7 @@
         <v>767</v>
       </c>
       <c r="D459" s="17" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="E459" s="17" t="s">
         <v>49</v>
@@ -34266,10 +34263,10 @@
         <v>55</v>
       </c>
       <c r="G459" s="17" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="H459" s="17" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="I459" s="4" t="s">
         <v>31</v>
@@ -34320,7 +34317,7 @@
         <v>767</v>
       </c>
       <c r="D460" s="17" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="E460" s="17" t="s">
         <v>49</v>
@@ -34329,10 +34326,10 @@
         <v>55</v>
       </c>
       <c r="G460" s="17" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="H460" s="17" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="I460" s="4" t="s">
         <v>31</v>
@@ -34385,7 +34382,7 @@
         <v>767</v>
       </c>
       <c r="D461" s="17" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="E461" s="17" t="s">
         <v>28</v>
@@ -34394,10 +34391,10 @@
         <v>55</v>
       </c>
       <c r="G461" s="17" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="H461" s="17" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="I461" s="4" t="s">
         <v>31</v>
@@ -34903,7 +34900,7 @@
         <v>779</v>
       </c>
       <c r="D469" s="17" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="E469" s="17" t="s">
         <v>49</v>
@@ -34912,10 +34909,10 @@
         <v>77</v>
       </c>
       <c r="G469" s="17" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="H469" s="17" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="I469" s="17" t="s">
         <v>84</v>
@@ -34966,7 +34963,7 @@
         <v>779</v>
       </c>
       <c r="D470" s="17" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="E470" s="17" t="s">
         <v>49</v>
@@ -34975,10 +34972,10 @@
         <v>319</v>
       </c>
       <c r="G470" s="17" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="H470" s="17" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I470" s="4" t="s">
         <v>31</v>
@@ -35297,7 +35294,7 @@
         <v>49</v>
       </c>
       <c r="F475" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G475" s="4" t="s">
         <v>796</v>
@@ -35421,19 +35418,19 @@
         <v>787</v>
       </c>
       <c r="D477" s="17" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="E477" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F477" s="17" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G477" s="17" t="s">
         <v>929</v>
       </c>
-      <c r="G477" s="17" t="s">
-        <v>930</v>
-      </c>
       <c r="H477" s="17" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I477" s="4" t="s">
         <v>31</v>
@@ -35486,19 +35483,19 @@
         <v>787</v>
       </c>
       <c r="D478" s="17" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="E478" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F478" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G478" s="17" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="H478" s="17" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="I478" s="17" t="s">
         <v>84</v>
@@ -35551,19 +35548,19 @@
         <v>787</v>
       </c>
       <c r="D479" s="17" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="E479" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F479" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G479" s="17" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="H479" s="17" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="I479" s="17" t="s">
         <v>84</v>
@@ -35616,7 +35613,7 @@
         <v>787</v>
       </c>
       <c r="D480" s="17" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="E480" s="17" t="s">
         <v>28</v>
@@ -35625,10 +35622,10 @@
         <v>55</v>
       </c>
       <c r="G480" s="17" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H480" s="17" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="I480" s="17" t="s">
         <v>51</v>
@@ -35876,7 +35873,7 @@
         <v>801</v>
       </c>
       <c r="D484" s="17" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="E484" s="17" t="s">
         <v>49</v>
@@ -35885,10 +35882,10 @@
         <v>282</v>
       </c>
       <c r="G484" s="17" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="H484" s="17" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="I484" s="17" t="s">
         <v>84</v>
@@ -35897,7 +35894,7 @@
         <v>913</v>
       </c>
       <c r="K484" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L484" s="13" t="s">
         <v>911</v>
@@ -35941,7 +35938,7 @@
         <v>801</v>
       </c>
       <c r="D485" s="17" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="E485" s="17" t="s">
         <v>49</v>
@@ -35950,10 +35947,10 @@
         <v>282</v>
       </c>
       <c r="G485" s="17" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="H485" s="17" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="I485" s="17" t="s">
         <v>84</v>
@@ -36006,7 +36003,7 @@
         <v>801</v>
       </c>
       <c r="D486" s="17" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="E486" s="17" t="s">
         <v>28</v>
@@ -36015,10 +36012,10 @@
         <v>282</v>
       </c>
       <c r="G486" s="17" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="H486" s="17" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="I486" s="17" t="s">
         <v>84</v>
@@ -36071,7 +36068,7 @@
         <v>801</v>
       </c>
       <c r="D487" s="17" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="E487" s="17" t="s">
         <v>49</v>
@@ -36080,10 +36077,10 @@
         <v>282</v>
       </c>
       <c r="G487" s="17" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="H487" s="17" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="I487" s="17" t="s">
         <v>84</v>
@@ -36133,7 +36130,7 @@
         <v>908</v>
       </c>
       <c r="C488" s="17" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="D488" s="3" t="s">
         <v>811</v>
@@ -36198,7 +36195,7 @@
         <v>908</v>
       </c>
       <c r="C489" s="17" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="D489" s="3" t="s">
         <v>813</v>
@@ -36263,7 +36260,7 @@
         <v>908</v>
       </c>
       <c r="C490" s="17" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="D490" s="3" t="s">
         <v>815</v>
@@ -36328,7 +36325,7 @@
         <v>908</v>
       </c>
       <c r="C491" s="17" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="D491" s="3" t="s">
         <v>817</v>
@@ -36393,7 +36390,7 @@
         <v>908</v>
       </c>
       <c r="C492" s="17" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="D492" s="3" t="s">
         <v>819</v>
@@ -36401,7 +36398,7 @@
       <c r="E492" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F492" s="4" t="s">
+      <c r="F492" s="17" t="s">
         <v>319</v>
       </c>
       <c r="G492" s="4" t="s">
@@ -36458,10 +36455,10 @@
         <v>923</v>
       </c>
       <c r="C493" s="17" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="D493" s="17" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="E493" s="17" t="s">
         <v>49</v>
@@ -36470,10 +36467,10 @@
         <v>348</v>
       </c>
       <c r="G493" s="17" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H493" s="17" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="I493" s="4" t="s">
         <v>31</v>
@@ -36523,10 +36520,10 @@
         <v>923</v>
       </c>
       <c r="C494" s="17" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D494" s="17" t="s">
         <v>1346</v>
-      </c>
-      <c r="D494" s="17" t="s">
-        <v>1348</v>
       </c>
       <c r="E494" s="17" t="s">
         <v>49</v>
@@ -36535,10 +36532,10 @@
         <v>348</v>
       </c>
       <c r="G494" s="17" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H494" s="17" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="I494" s="4" t="s">
         <v>31</v>
@@ -36588,10 +36585,10 @@
         <v>923</v>
       </c>
       <c r="C495" s="17" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="D495" s="17" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="E495" s="17" t="s">
         <v>49</v>
@@ -36600,10 +36597,10 @@
         <v>348</v>
       </c>
       <c r="G495" s="17" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H495" s="17" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="I495" s="4" t="s">
         <v>31</v>
@@ -36653,10 +36650,10 @@
         <v>923</v>
       </c>
       <c r="C496" s="17" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="D496" s="17" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="E496" s="17" t="s">
         <v>28</v>
@@ -36665,10 +36662,10 @@
         <v>348</v>
       </c>
       <c r="G496" s="17" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H496" s="17" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="I496" s="4" t="s">
         <v>31</v>
@@ -36721,7 +36718,7 @@
         <v>821</v>
       </c>
       <c r="D497" s="17" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="E497" s="17" t="s">
         <v>49</v>
@@ -36730,10 +36727,10 @@
         <v>141</v>
       </c>
       <c r="G497" s="17" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="H497" s="17" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="I497" s="4" t="s">
         <v>31</v>
@@ -36774,7 +36771,7 @@
         <v>821</v>
       </c>
       <c r="D498" s="17" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="E498" s="17" t="s">
         <v>28</v>
@@ -36839,7 +36836,7 @@
         <v>821</v>
       </c>
       <c r="D499" s="17" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="E499" s="17" t="s">
         <v>49</v>
@@ -36904,7 +36901,7 @@
         <v>821</v>
       </c>
       <c r="D500" s="17" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="E500" s="17" t="s">
         <v>49</v>
@@ -36913,10 +36910,10 @@
         <v>141</v>
       </c>
       <c r="G500" s="4" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="H500" s="4" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="I500" s="17" t="s">
         <v>84</v>
@@ -37292,7 +37289,7 @@
         <v>49</v>
       </c>
       <c r="F506" s="17" t="s">
-        <v>929</v>
+        <v>1450</v>
       </c>
       <c r="G506" s="4" t="s">
         <v>70</v>
@@ -37481,7 +37478,7 @@
         <v>826</v>
       </c>
       <c r="D509" s="17" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="E509" s="17" t="s">
         <v>28</v>
@@ -37490,10 +37487,10 @@
         <v>65</v>
       </c>
       <c r="G509" s="17" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="H509" s="17" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="I509" s="4" t="s">
         <v>31</v>
@@ -37544,7 +37541,7 @@
         <v>826</v>
       </c>
       <c r="D510" s="17" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="E510" s="17" t="s">
         <v>49</v>
@@ -37553,10 +37550,10 @@
         <v>77</v>
       </c>
       <c r="G510" s="17" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="H510" s="17" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="I510" s="17" t="s">
         <v>84</v>
@@ -37607,7 +37604,7 @@
         <v>826</v>
       </c>
       <c r="D511" s="17" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="E511" s="17" t="s">
         <v>49</v>
@@ -37616,10 +37613,10 @@
         <v>77</v>
       </c>
       <c r="G511" s="17" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H511" s="17" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="I511" s="4" t="s">
         <v>31</v>
@@ -37664,7 +37661,7 @@
         <v>826</v>
       </c>
       <c r="D512" s="17" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="E512" s="17" t="s">
         <v>49</v>
@@ -37673,10 +37670,10 @@
         <v>40</v>
       </c>
       <c r="G512" s="17" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="H512" s="17" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="I512" s="4" t="s">
         <v>31</v>
@@ -37729,19 +37726,19 @@
         <v>826</v>
       </c>
       <c r="D513" s="17" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="E513" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F513" s="17" t="s">
-        <v>991</v>
+        <v>171</v>
       </c>
       <c r="G513" s="17" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="H513" s="17" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="I513" s="4" t="s">
         <v>31</v>
@@ -37794,7 +37791,7 @@
         <v>826</v>
       </c>
       <c r="D514" s="17" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="E514" s="17" t="s">
         <v>49</v>
@@ -37803,7 +37800,7 @@
         <v>77</v>
       </c>
       <c r="G514" s="17" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="H514" s="17" t="s">
         <v>886</v>
@@ -37856,7 +37853,7 @@
         <v>908</v>
       </c>
       <c r="C515" s="17" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="D515" s="3" t="s">
         <v>842</v>
@@ -37921,7 +37918,7 @@
         <v>908</v>
       </c>
       <c r="C516" s="17" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="D516" s="3" t="s">
         <v>844</v>
@@ -37986,10 +37983,10 @@
         <v>923</v>
       </c>
       <c r="C517" s="17" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="D517" s="17" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="E517" s="17" t="s">
         <v>28</v>
@@ -37998,7 +37995,7 @@
         <v>77</v>
       </c>
       <c r="G517" s="17" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="H517" s="17" t="s">
         <v>886</v>
@@ -38049,10 +38046,10 @@
         <v>923</v>
       </c>
       <c r="C518" s="17" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D518" s="17" t="s">
         <v>1368</v>
-      </c>
-      <c r="D518" s="17" t="s">
-        <v>1370</v>
       </c>
       <c r="E518" s="17" t="s">
         <v>49</v>
@@ -38061,10 +38058,10 @@
         <v>319</v>
       </c>
       <c r="G518" s="17" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="H518" s="17" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="I518" s="17" t="s">
         <v>84</v>
@@ -38114,22 +38111,22 @@
         <v>923</v>
       </c>
       <c r="C519" s="17" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="D519" s="17" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="E519" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F519" s="17" t="s">
-        <v>991</v>
+        <v>171</v>
       </c>
       <c r="G519" s="17" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="H519" s="17" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="I519" s="17" t="s">
         <v>84</v>
@@ -38138,7 +38135,7 @@
         <v>794</v>
       </c>
       <c r="K519" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L519" s="13" t="s">
         <v>794</v>
@@ -38177,10 +38174,10 @@
         <v>923</v>
       </c>
       <c r="C520" s="17" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="D520" s="17" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="E520" s="17" t="s">
         <v>49</v>
@@ -38189,10 +38186,10 @@
         <v>77</v>
       </c>
       <c r="G520" s="17" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="H520" s="17" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="I520" s="17" t="s">
         <v>84</v>
@@ -38242,7 +38239,7 @@
         <v>908</v>
       </c>
       <c r="C521" s="17" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="D521" s="3" t="s">
         <v>847</v>
@@ -38305,7 +38302,7 @@
         <v>908</v>
       </c>
       <c r="C522" s="17" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="D522" s="3" t="s">
         <v>849</v>
@@ -38368,7 +38365,7 @@
         <v>908</v>
       </c>
       <c r="C523" s="17" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="D523" s="3" t="s">
         <v>852</v>
@@ -38433,10 +38430,10 @@
         <v>923</v>
       </c>
       <c r="C524" s="17" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="D524" s="17" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="E524" s="17" t="s">
         <v>49</v>
@@ -38445,10 +38442,10 @@
         <v>96</v>
       </c>
       <c r="G524" s="17" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="H524" s="17" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="I524" s="17" t="s">
         <v>84</v>
@@ -38498,10 +38495,10 @@
         <v>923</v>
       </c>
       <c r="C525" s="17" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="D525" s="17" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="E525" s="17" t="s">
         <v>49</v>
@@ -38510,10 +38507,10 @@
         <v>96</v>
       </c>
       <c r="G525" s="17" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="H525" s="17" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="I525" s="17" t="s">
         <v>84</v>
@@ -38561,22 +38558,22 @@
         <v>923</v>
       </c>
       <c r="C526" s="17" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="D526" s="17" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="E526" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F526" s="17" t="s">
-        <v>991</v>
+        <v>171</v>
       </c>
       <c r="G526" s="17" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="H526" s="17" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="I526" s="4" t="s">
         <v>31</v>
@@ -38626,7 +38623,7 @@
         <v>908</v>
       </c>
       <c r="C527" s="17" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="D527" s="3" t="s">
         <v>854</v>
@@ -38691,7 +38688,7 @@
         <v>908</v>
       </c>
       <c r="C528" s="17" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="D528" s="3" t="s">
         <v>856</v>
@@ -38754,7 +38751,7 @@
         <v>908</v>
       </c>
       <c r="C529" s="17" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="D529" s="3" t="s">
         <v>857</v>
@@ -38819,7 +38816,7 @@
         <v>908</v>
       </c>
       <c r="C530" s="17" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="D530" s="3" t="s">
         <v>859</v>
@@ -38884,10 +38881,10 @@
         <v>923</v>
       </c>
       <c r="C531" s="17" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="D531" s="17" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="E531" s="17" t="s">
         <v>49</v>
@@ -38947,10 +38944,10 @@
         <v>923</v>
       </c>
       <c r="C532" s="17" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D532" s="17" t="s">
         <v>1382</v>
-      </c>
-      <c r="D532" s="17" t="s">
-        <v>1384</v>
       </c>
       <c r="E532" s="17" t="s">
         <v>49</v>
@@ -39010,10 +39007,10 @@
         <v>923</v>
       </c>
       <c r="C533" s="17" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="D533" s="17" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="E533" s="17" t="s">
         <v>49</v>
@@ -39022,10 +39019,10 @@
         <v>96</v>
       </c>
       <c r="G533" s="17" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="H533" s="17" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="I533" s="17" t="s">
         <v>84</v>
@@ -39073,10 +39070,10 @@
         <v>923</v>
       </c>
       <c r="C534" s="17" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="D534" s="17" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="E534" s="17" t="s">
         <v>49</v>
@@ -39085,10 +39082,10 @@
         <v>110</v>
       </c>
       <c r="G534" s="17" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="H534" s="17" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="I534" s="17" t="s">
         <v>84</v>
@@ -39136,10 +39133,10 @@
         <v>923</v>
       </c>
       <c r="C535" s="17" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="D535" s="17" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="E535" s="17" t="s">
         <v>49</v>
@@ -39148,10 +39145,10 @@
         <v>110</v>
       </c>
       <c r="G535" s="17" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="H535" s="17" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="I535" s="4" t="s">
         <v>31</v>
@@ -39199,10 +39196,10 @@
         <v>923</v>
       </c>
       <c r="C536" s="17" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="D536" s="17" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="E536" s="17" t="s">
         <v>49</v>
@@ -39214,7 +39211,7 @@
         <v>876</v>
       </c>
       <c r="H536" s="17" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="I536" s="4" t="s">
         <v>31</v>
@@ -39389,7 +39386,7 @@
         <v>860</v>
       </c>
       <c r="D539" s="17" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="E539" s="17" t="s">
         <v>49</v>
@@ -39398,10 +39395,10 @@
         <v>77</v>
       </c>
       <c r="G539" s="17" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="H539" s="17" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="I539" s="4" t="s">
         <v>31</v>
@@ -39442,7 +39439,7 @@
         <v>860</v>
       </c>
       <c r="D540" s="17" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="E540" s="17" t="s">
         <v>28</v>
@@ -39451,10 +39448,10 @@
         <v>77</v>
       </c>
       <c r="G540" s="17" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="H540" s="17" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="I540" s="4" t="s">
         <v>31</v>
@@ -39507,7 +39504,7 @@
         <v>860</v>
       </c>
       <c r="D541" s="17" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="E541" s="17" t="s">
         <v>49</v>
@@ -39516,10 +39513,10 @@
         <v>77</v>
       </c>
       <c r="G541" s="17" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="H541" s="17" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="I541" s="4" t="s">
         <v>31</v>
@@ -39569,7 +39566,7 @@
         <v>908</v>
       </c>
       <c r="C542" s="17" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="D542" s="3" t="s">
         <v>867</v>
@@ -39634,7 +39631,7 @@
         <v>908</v>
       </c>
       <c r="C543" s="17" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="D543" s="3" t="s">
         <v>871</v>
@@ -40285,7 +40282,7 @@
         <v>873</v>
       </c>
       <c r="D553" s="17" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="E553" s="17" t="s">
         <v>49</v>
@@ -40294,10 +40291,10 @@
         <v>348</v>
       </c>
       <c r="G553" s="17" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="H553" s="17" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="I553" s="17" t="s">
         <v>84</v>
@@ -40350,7 +40347,7 @@
         <v>873</v>
       </c>
       <c r="D554" s="17" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="E554" s="17" t="s">
         <v>49</v>
@@ -40359,10 +40356,10 @@
         <v>65</v>
       </c>
       <c r="G554" s="17" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="H554" s="17" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="I554" s="4" t="s">
         <v>31</v>
@@ -40371,7 +40368,7 @@
         <v>794</v>
       </c>
       <c r="K554" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L554" s="13" t="s">
         <v>794</v>
@@ -40415,7 +40412,7 @@
         <v>873</v>
       </c>
       <c r="D555" s="17" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="E555" s="17" t="s">
         <v>49</v>
@@ -40424,10 +40421,10 @@
         <v>265</v>
       </c>
       <c r="G555" s="17" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="H555" s="17" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="I555" s="4" t="s">
         <v>31</v>
@@ -40480,7 +40477,7 @@
         <v>873</v>
       </c>
       <c r="D556" s="17" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="E556" s="17" t="s">
         <v>49</v>
@@ -40501,7 +40498,7 @@
         <v>794</v>
       </c>
       <c r="K556" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L556" s="13" t="s">
         <v>794</v>
@@ -40545,19 +40542,19 @@
         <v>873</v>
       </c>
       <c r="D557" s="17" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="E557" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F557" s="17" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G557" s="17" t="s">
         <v>929</v>
       </c>
-      <c r="G557" s="17" t="s">
-        <v>930</v>
-      </c>
       <c r="H557" s="17" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I557" s="4" t="s">
         <v>31</v>
@@ -40610,7 +40607,7 @@
         <v>873</v>
       </c>
       <c r="D558" s="17" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="E558" s="17" t="s">
         <v>49</v>
@@ -40619,10 +40616,10 @@
         <v>40</v>
       </c>
       <c r="G558" s="17" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="H558" s="17" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="I558" s="4" t="s">
         <v>31</v>
@@ -40675,19 +40672,19 @@
         <v>873</v>
       </c>
       <c r="D559" s="17" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="E559" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F559" s="17" t="s">
-        <v>991</v>
+        <v>171</v>
       </c>
       <c r="G559" s="17" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="H559" s="17" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="I559" s="4" t="s">
         <v>31</v>
@@ -40740,19 +40737,19 @@
         <v>873</v>
       </c>
       <c r="D560" s="17" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="E560" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F560" s="17" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G560" s="17" t="s">
         <v>929</v>
       </c>
-      <c r="G560" s="17" t="s">
-        <v>930</v>
-      </c>
       <c r="H560" s="17" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I560" s="4" t="s">
         <v>31</v>
@@ -40761,7 +40758,7 @@
         <v>794</v>
       </c>
       <c r="K560" s="17" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L560" s="13" t="s">
         <v>794</v>
@@ -40805,7 +40802,7 @@
         <v>873</v>
       </c>
       <c r="D561" s="17" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="E561" s="17" t="s">
         <v>49</v>
@@ -40814,10 +40811,10 @@
         <v>348</v>
       </c>
       <c r="G561" s="17" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="H561" s="17" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="I561" s="17" t="s">
         <v>84</v>
@@ -40865,10 +40862,10 @@
         <v>923</v>
       </c>
       <c r="C562" s="17" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="D562" s="17" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="E562" s="17" t="s">
         <v>49</v>
@@ -40877,10 +40874,10 @@
         <v>869</v>
       </c>
       <c r="G562" s="17" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H562" s="17" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="I562" s="17" t="s">
         <v>84</v>
@@ -40928,10 +40925,10 @@
         <v>923</v>
       </c>
       <c r="C563" s="17" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="D563" s="17" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="E563" s="17" t="s">
         <v>49</v>
@@ -40940,10 +40937,10 @@
         <v>869</v>
       </c>
       <c r="G563" s="17" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H563" s="17" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="I563" s="17" t="s">
         <v>84</v>
@@ -40993,10 +40990,10 @@
         <v>923</v>
       </c>
       <c r="C564" s="17" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="D564" s="17" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="E564" s="17" t="s">
         <v>49</v>
@@ -41005,10 +41002,10 @@
         <v>869</v>
       </c>
       <c r="G564" s="17" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H564" s="17" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="I564" s="17" t="s">
         <v>84</v>
@@ -41058,10 +41055,10 @@
         <v>923</v>
       </c>
       <c r="C565" s="17" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="D565" s="17" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="E565" s="17" t="s">
         <v>49</v>
@@ -41070,10 +41067,10 @@
         <v>869</v>
       </c>
       <c r="G565" s="17" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H565" s="17" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="I565" s="17" t="s">
         <v>84</v>
@@ -41196,8 +41193,8 @@
       <c r="E567" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F567" s="4" t="s">
-        <v>513</v>
+      <c r="F567" s="17" t="s">
+        <v>511</v>
       </c>
       <c r="G567" s="4" t="s">
         <v>906</v>
@@ -41256,7 +41253,7 @@
         <v>900</v>
       </c>
       <c r="D568" s="17" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="E568" s="17" t="s">
         <v>49</v>
@@ -41265,10 +41262,10 @@
         <v>186</v>
       </c>
       <c r="G568" s="17" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="H568" s="17" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="I568" s="17" t="s">
         <v>84</v>
@@ -41321,7 +41318,7 @@
         <v>900</v>
       </c>
       <c r="D569" s="17" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="E569" s="17" t="s">
         <v>49</v>
@@ -41330,10 +41327,10 @@
         <v>186</v>
       </c>
       <c r="G569" s="17" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="H569" s="17" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="I569" s="17" t="s">
         <v>84</v>
@@ -41386,7 +41383,7 @@
         <v>900</v>
       </c>
       <c r="D570" s="17" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="E570" s="17" t="s">
         <v>49</v>
@@ -41395,10 +41392,10 @@
         <v>186</v>
       </c>
       <c r="G570" s="17" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="H570" s="17" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="I570" s="17" t="s">
         <v>84</v>
@@ -41451,7 +41448,7 @@
         <v>900</v>
       </c>
       <c r="D571" s="17" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="E571" s="17" t="s">
         <v>49</v>
@@ -41460,10 +41457,10 @@
         <v>186</v>
       </c>
       <c r="G571" s="17" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="H571" s="17" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="I571" s="17" t="s">
         <v>84</v>
@@ -43717,7 +43714,7 @@
     </row>
     <row r="7" spans="1:8" ht="78" customHeight="1">
       <c r="A7" s="23" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>26</v>
@@ -43739,13 +43736,13 @@
     </row>
     <row r="8" spans="1:8" ht="78" customHeight="1">
       <c r="A8" s="23" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>39</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="D8" s="25">
         <v>600000</v>
@@ -43761,7 +43758,7 @@
     </row>
     <row r="9" spans="1:8" ht="78" customHeight="1">
       <c r="A9" s="23" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B9" s="24" t="s">
         <v>47</v>
@@ -43785,10 +43782,10 @@
     </row>
     <row r="10" spans="1:8" ht="78" customHeight="1">
       <c r="A10" s="23" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="C10" s="24" t="s">
         <v>227</v>
@@ -43809,7 +43806,7 @@
     </row>
     <row r="11" spans="1:8" ht="78" customHeight="1">
       <c r="A11" s="23" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>229</v>
@@ -43833,7 +43830,7 @@
     </row>
     <row r="12" spans="1:8" ht="78" customHeight="1">
       <c r="A12" s="23" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>231</v>
@@ -43855,10 +43852,10 @@
     </row>
     <row r="13" spans="1:8" ht="78" customHeight="1">
       <c r="A13" s="23" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B13" s="24" t="s">
         <v>1424</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>1426</v>
       </c>
       <c r="C13" s="24" t="s">
         <v>235</v>
@@ -44087,7 +44084,7 @@
     </row>
     <row r="22" spans="1:8" ht="78" customHeight="1">
       <c r="A22" s="23" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>114</v>
@@ -44113,7 +44110,7 @@
     </row>
     <row r="23" spans="1:8" ht="78" customHeight="1">
       <c r="A23" s="23" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B23" s="24" t="s">
         <v>118</v>
@@ -44135,7 +44132,7 @@
     </row>
     <row r="24" spans="1:8" ht="78" customHeight="1">
       <c r="A24" s="23" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B24" s="24" t="s">
         <v>120</v>
@@ -44157,7 +44154,7 @@
     </row>
     <row r="25" spans="1:8" ht="78" customHeight="1">
       <c r="A25" s="23" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B25" s="24" t="s">
         <v>122</v>
@@ -44335,7 +44332,7 @@
     </row>
     <row r="32" spans="1:8" ht="78" customHeight="1">
       <c r="A32" s="23" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B32" s="24" t="s">
         <v>176</v>
@@ -44361,7 +44358,7 @@
     </row>
     <row r="33" spans="1:8" ht="78" customHeight="1">
       <c r="A33" s="23" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B33" s="24" t="s">
         <v>179</v>
@@ -44387,7 +44384,7 @@
     </row>
     <row r="34" spans="1:8" ht="78" customHeight="1">
       <c r="A34" s="23" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B34" s="24" t="s">
         <v>184</v>
@@ -44413,7 +44410,7 @@
     </row>
     <row r="35" spans="1:8" ht="78" customHeight="1">
       <c r="A35" s="23" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B35" s="24" t="s">
         <v>188</v>
@@ -44439,7 +44436,7 @@
     </row>
     <row r="36" spans="1:8" ht="78" customHeight="1">
       <c r="A36" s="23" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B36" s="24" t="s">
         <v>192</v>
@@ -44543,7 +44540,7 @@
     </row>
     <row r="40" spans="1:8" ht="78" customHeight="1">
       <c r="A40" s="23" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B40" s="24" t="s">
         <v>156</v>
@@ -44569,7 +44566,7 @@
     </row>
     <row r="41" spans="1:8" ht="78" customHeight="1">
       <c r="A41" s="23" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B41" s="24" t="s">
         <v>158</v>
@@ -44595,7 +44592,7 @@
     </row>
     <row r="42" spans="1:8" ht="78" customHeight="1">
       <c r="A42" s="23" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B42" s="24" t="s">
         <v>160</v>
@@ -44621,7 +44618,7 @@
     </row>
     <row r="43" spans="1:8" ht="78" customHeight="1">
       <c r="A43" s="23" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B43" s="24" t="s">
         <v>162</v>
@@ -44647,7 +44644,7 @@
     </row>
     <row r="44" spans="1:8" ht="78" customHeight="1">
       <c r="A44" s="23" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B44" s="24" t="s">
         <v>164</v>
@@ -44673,7 +44670,7 @@
     </row>
     <row r="45" spans="1:8" ht="78" customHeight="1">
       <c r="A45" s="23" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B45" s="24" t="s">
         <v>166</v>
@@ -44751,7 +44748,7 @@
     </row>
     <row r="48" spans="1:8" ht="78" customHeight="1">
       <c r="A48" s="23" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="B48" s="24" t="s">
         <v>214</v>
@@ -44777,7 +44774,7 @@
     </row>
     <row r="49" spans="1:8" ht="78" customHeight="1">
       <c r="A49" s="23" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="B49" s="24" t="s">
         <v>217</v>
@@ -44803,7 +44800,7 @@
     </row>
     <row r="50" spans="1:8" ht="78" customHeight="1">
       <c r="A50" s="23" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="B50" s="24" t="s">
         <v>219</v>
@@ -44829,7 +44826,7 @@
     </row>
     <row r="51" spans="1:8" ht="78" customHeight="1">
       <c r="A51" s="23" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="B51" s="24" t="s">
         <v>222</v>
@@ -44885,7 +44882,7 @@
         <v>199</v>
       </c>
       <c r="C53" s="24" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="D53" s="27"/>
       <c r="E53" s="25">
@@ -44951,7 +44948,7 @@
     </row>
     <row r="56" spans="1:8" ht="78" customHeight="1">
       <c r="A56" s="23" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="B56" s="24" t="s">
         <v>207</v>
@@ -44977,7 +44974,7 @@
     </row>
     <row r="57" spans="1:8" ht="78" customHeight="1">
       <c r="A57" s="23" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="B57" s="24" t="s">
         <v>210</v>
@@ -45003,7 +45000,7 @@
     </row>
     <row r="58" spans="1:8" ht="78" customHeight="1">
       <c r="A58" s="23" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="B58" s="24" t="s">
         <v>237</v>
@@ -45029,7 +45026,7 @@
     </row>
     <row r="59" spans="1:8" ht="78" customHeight="1">
       <c r="A59" s="23" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="B59" s="24" t="s">
         <v>240</v>
@@ -45055,7 +45052,7 @@
     </row>
     <row r="60" spans="1:8" ht="78" customHeight="1">
       <c r="A60" s="23" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="B60" s="24" t="s">
         <v>242</v>
@@ -45081,7 +45078,7 @@
     </row>
     <row r="61" spans="1:8" ht="78" customHeight="1">
       <c r="A61" s="23" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B61" s="24" t="s">
         <v>245</v>
@@ -45107,7 +45104,7 @@
     </row>
     <row r="62" spans="1:8" ht="78" customHeight="1">
       <c r="A62" s="23" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B62" s="24" t="s">
         <v>248</v>
@@ -45133,7 +45130,7 @@
     </row>
     <row r="63" spans="1:8" ht="78" customHeight="1">
       <c r="A63" s="23" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B63" s="24" t="s">
         <v>251</v>
@@ -45159,7 +45156,7 @@
     </row>
     <row r="64" spans="1:8" ht="78" customHeight="1">
       <c r="A64" s="23" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B64" s="24" t="s">
         <v>252</v>
@@ -45185,7 +45182,7 @@
     </row>
     <row r="65" spans="1:8" ht="78" customHeight="1">
       <c r="A65" s="23" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B65" s="24" t="s">
         <v>256</v>
@@ -45214,7 +45211,7 @@
         <v>258</v>
       </c>
       <c r="B66" s="24" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="C66" s="24" t="s">
         <v>260</v>
@@ -45234,7 +45231,7 @@
         <v>258</v>
       </c>
       <c r="B67" s="24" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="C67" s="24" t="s">
         <v>264</v>
@@ -45254,7 +45251,7 @@
         <v>258</v>
       </c>
       <c r="B68" s="24" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="C68" s="24" t="s">
         <v>268</v>
@@ -45274,7 +45271,7 @@
         <v>258</v>
       </c>
       <c r="B69" s="24" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="C69" s="24" t="s">
         <v>272</v>
@@ -45294,7 +45291,7 @@
         <v>258</v>
       </c>
       <c r="B70" s="24" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="C70" s="24" t="s">
         <v>275</v>
@@ -45314,7 +45311,7 @@
         <v>258</v>
       </c>
       <c r="B71" s="24" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="C71" s="24" t="s">
         <v>277</v>
@@ -45331,7 +45328,7 @@
     </row>
     <row r="72" spans="1:8" ht="78" customHeight="1">
       <c r="A72" s="23" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B72" s="24" t="s">
         <v>286</v>
@@ -45357,7 +45354,7 @@
     </row>
     <row r="73" spans="1:8" ht="78" customHeight="1">
       <c r="A73" s="23" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B73" s="24" t="s">
         <v>289</v>
@@ -45383,7 +45380,7 @@
     </row>
     <row r="74" spans="1:8" ht="78" customHeight="1">
       <c r="A74" s="23" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B74" s="24" t="s">
         <v>291</v>
@@ -45409,7 +45406,7 @@
     </row>
     <row r="75" spans="1:8" ht="78" customHeight="1">
       <c r="A75" s="23" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B75" s="24" t="s">
         <v>293</v>
@@ -45435,7 +45432,7 @@
     </row>
     <row r="76" spans="1:8" ht="78" customHeight="1">
       <c r="A76" s="23" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B76" s="24" t="s">
         <v>295</v>
@@ -45461,7 +45458,7 @@
     </row>
     <row r="77" spans="1:8" ht="78" customHeight="1">
       <c r="A77" s="23" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B77" s="24" t="s">
         <v>298</v>
@@ -45487,7 +45484,7 @@
     </row>
     <row r="78" spans="1:8" ht="78" customHeight="1">
       <c r="A78" s="23" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B78" s="24" t="s">
         <v>301</v>
@@ -45513,7 +45510,7 @@
     </row>
     <row r="79" spans="1:8" ht="78" customHeight="1">
       <c r="A79" s="23" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B79" s="24" t="s">
         <v>304</v>
@@ -45664,7 +45661,7 @@
         <v>600000</v>
       </c>
       <c r="H84" s="25" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="78" customHeight="1">
@@ -45747,7 +45744,7 @@
     </row>
     <row r="88" spans="1:8" ht="78" customHeight="1">
       <c r="A88" s="23" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="B88" s="24" t="s">
         <v>380</v>
@@ -45773,7 +45770,7 @@
     </row>
     <row r="89" spans="1:8" ht="78" customHeight="1">
       <c r="A89" s="23" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="B89" s="24" t="s">
         <v>382</v>
@@ -45799,7 +45796,7 @@
     </row>
     <row r="90" spans="1:8" ht="78" customHeight="1">
       <c r="A90" s="23" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="B90" s="24" t="s">
         <v>385</v>
@@ -45825,7 +45822,7 @@
     </row>
     <row r="91" spans="1:8" ht="78" customHeight="1">
       <c r="A91" s="23" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="B91" s="24" t="s">
         <v>387</v>
@@ -45851,7 +45848,7 @@
     </row>
     <row r="92" spans="1:8" ht="78" customHeight="1">
       <c r="A92" s="23" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B92" s="24" t="s">
         <v>337</v>
@@ -45877,7 +45874,7 @@
     </row>
     <row r="93" spans="1:8" ht="78" customHeight="1">
       <c r="A93" s="23" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B93" s="24" t="s">
         <v>342</v>
@@ -45903,7 +45900,7 @@
     </row>
     <row r="94" spans="1:8" ht="78" customHeight="1">
       <c r="A94" s="23" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B94" s="24" t="s">
         <v>346</v>
@@ -45929,7 +45926,7 @@
     </row>
     <row r="95" spans="1:8" ht="78" customHeight="1">
       <c r="A95" s="23" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B95" s="24" t="s">
         <v>351</v>
@@ -45955,7 +45952,7 @@
     </row>
     <row r="96" spans="1:8" ht="78" customHeight="1">
       <c r="A96" s="23" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B96" s="24" t="s">
         <v>354</v>
@@ -45981,7 +45978,7 @@
     </row>
     <row r="97" spans="1:8" ht="78" customHeight="1">
       <c r="A97" s="23" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B97" s="24" t="s">
         <v>356</v>
@@ -46163,7 +46160,7 @@
     </row>
     <row r="104" spans="1:8" ht="78" customHeight="1">
       <c r="A104" s="23" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="B104" s="24" t="s">
         <v>390</v>
@@ -46189,7 +46186,7 @@
     </row>
     <row r="105" spans="1:8" ht="78" customHeight="1">
       <c r="A105" s="23" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="B105" s="24" t="s">
         <v>394</v>
@@ -46215,7 +46212,7 @@
     </row>
     <row r="106" spans="1:8" ht="78" customHeight="1">
       <c r="A106" s="23" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="B106" s="24" t="s">
         <v>396</v>
@@ -46241,7 +46238,7 @@
     </row>
     <row r="107" spans="1:8" ht="78" customHeight="1">
       <c r="A107" s="23" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="B107" s="24" t="s">
         <v>398</v>
@@ -46267,7 +46264,7 @@
     </row>
     <row r="108" spans="1:8" ht="78" customHeight="1">
       <c r="A108" s="23" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="B108" s="24" t="s">
         <v>401</v>
@@ -46289,7 +46286,7 @@
     </row>
     <row r="109" spans="1:8" ht="78" customHeight="1">
       <c r="A109" s="23" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="B109" s="24" t="s">
         <v>404</v>
@@ -46311,7 +46308,7 @@
     </row>
     <row r="110" spans="1:8" ht="78" customHeight="1">
       <c r="A110" s="23" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="B110" s="24" t="s">
         <v>406</v>
@@ -46333,7 +46330,7 @@
     </row>
     <row r="111" spans="1:8" ht="78" customHeight="1">
       <c r="A111" s="23" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="B111" s="24" t="s">
         <v>408</v>
@@ -46511,7 +46508,7 @@
     </row>
     <row r="118" spans="1:8" ht="78" customHeight="1">
       <c r="A118" s="23" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="B118" s="24" t="s">
         <v>446</v>
@@ -46537,7 +46534,7 @@
     </row>
     <row r="119" spans="1:8" ht="78" customHeight="1">
       <c r="A119" s="23" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="B119" s="24" t="s">
         <v>450</v>
@@ -46563,7 +46560,7 @@
     </row>
     <row r="120" spans="1:8" ht="78" customHeight="1">
       <c r="A120" s="23" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="B120" s="24" t="s">
         <v>454</v>
@@ -46589,7 +46586,7 @@
     </row>
     <row r="121" spans="1:8" ht="78" customHeight="1">
       <c r="A121" s="23" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="B121" s="24" t="s">
         <v>458</v>
@@ -46615,7 +46612,7 @@
     </row>
     <row r="122" spans="1:8" ht="78" customHeight="1">
       <c r="A122" s="23" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="B122" s="24" t="s">
         <v>462</v>
@@ -46641,10 +46638,10 @@
     </row>
     <row r="123" spans="1:8" ht="78" customHeight="1">
       <c r="A123" s="23" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="B123" s="24" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="C123" s="24" t="s">
         <v>466</v>
@@ -46667,7 +46664,7 @@
     </row>
     <row r="124" spans="1:8" ht="78" customHeight="1">
       <c r="A124" s="23" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="B124" s="24" t="s">
         <v>469</v>
@@ -46823,7 +46820,7 @@
     </row>
     <row r="130" spans="1:8" ht="78" customHeight="1">
       <c r="A130" s="23" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B130" s="24" t="s">
         <v>489</v>
@@ -46849,7 +46846,7 @@
     </row>
     <row r="131" spans="1:8" ht="78" customHeight="1">
       <c r="A131" s="23" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B131" s="24" t="s">
         <v>492</v>
@@ -46875,7 +46872,7 @@
     </row>
     <row r="132" spans="1:8" ht="78" customHeight="1">
       <c r="A132" s="23" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B132" s="24" t="s">
         <v>494</v>
@@ -46901,7 +46898,7 @@
     </row>
     <row r="133" spans="1:8" ht="78" customHeight="1">
       <c r="A133" s="23" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B133" s="24" t="s">
         <v>496</v>
@@ -46927,7 +46924,7 @@
     </row>
     <row r="134" spans="1:8" ht="78" customHeight="1">
       <c r="A134" s="23" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B134" s="24" t="s">
         <v>498</v>
@@ -46953,7 +46950,7 @@
     </row>
     <row r="135" spans="1:8" ht="78" customHeight="1">
       <c r="A135" s="23" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B135" s="24" t="s">
         <v>501</v>
@@ -46979,7 +46976,7 @@
     </row>
     <row r="136" spans="1:8" ht="78" customHeight="1">
       <c r="A136" s="23" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B136" s="24" t="s">
         <v>505</v>
@@ -47187,7 +47184,7 @@
     </row>
     <row r="144" spans="1:8" ht="78" customHeight="1">
       <c r="A144" s="23" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="B144" s="24" t="s">
         <v>559</v>
@@ -47213,7 +47210,7 @@
     </row>
     <row r="145" spans="1:8" ht="78" customHeight="1">
       <c r="A145" s="23" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="B145" s="24" t="s">
         <v>562</v>
@@ -47239,7 +47236,7 @@
     </row>
     <row r="146" spans="1:8" ht="78" customHeight="1">
       <c r="A146" s="23" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="B146" s="24" t="s">
         <v>564</v>
@@ -47265,7 +47262,7 @@
     </row>
     <row r="147" spans="1:8" ht="78" customHeight="1">
       <c r="A147" s="23" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="B147" s="24" t="s">
         <v>566</v>
@@ -47291,7 +47288,7 @@
     </row>
     <row r="148" spans="1:8" ht="78" customHeight="1">
       <c r="A148" s="23" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="B148" s="24" t="s">
         <v>569</v>
@@ -47317,7 +47314,7 @@
     </row>
     <row r="149" spans="1:8" ht="78" customHeight="1">
       <c r="A149" s="23" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="B149" s="24" t="s">
         <v>570</v>
@@ -47341,7 +47338,7 @@
     </row>
     <row r="150" spans="1:8" ht="78" customHeight="1">
       <c r="A150" s="23" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="B150" s="24" t="s">
         <v>572</v>
@@ -47445,7 +47442,7 @@
     </row>
     <row r="154" spans="1:8" ht="78" customHeight="1">
       <c r="A154" s="23" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B154" s="24" t="s">
         <v>510</v>
@@ -47471,7 +47468,7 @@
     </row>
     <row r="155" spans="1:8" ht="78" customHeight="1">
       <c r="A155" s="23" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B155" s="24" t="s">
         <v>514</v>
@@ -47497,7 +47494,7 @@
     </row>
     <row r="156" spans="1:8" ht="78" customHeight="1">
       <c r="A156" s="23" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B156" s="24" t="s">
         <v>517</v>
@@ -47523,7 +47520,7 @@
     </row>
     <row r="157" spans="1:8" ht="78" customHeight="1">
       <c r="A157" s="23" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B157" s="24" t="s">
         <v>518</v>
@@ -47581,7 +47578,7 @@
     </row>
     <row r="160" spans="1:8" ht="78" customHeight="1">
       <c r="A160" s="23" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="B160" s="24" t="s">
         <v>576</v>
@@ -47607,7 +47604,7 @@
     </row>
     <row r="161" spans="1:8" ht="78" customHeight="1">
       <c r="A161" s="23" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="B161" s="24" t="s">
         <v>578</v>
@@ -47633,7 +47630,7 @@
     </row>
     <row r="162" spans="1:8" ht="78" customHeight="1">
       <c r="A162" s="23" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="B162" s="24" t="s">
         <v>581</v>
@@ -47919,7 +47916,7 @@
     </row>
     <row r="173" spans="1:8" ht="78" customHeight="1">
       <c r="A173" s="23" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B173" s="24" t="s">
         <v>607</v>
@@ -47941,7 +47938,7 @@
     </row>
     <row r="174" spans="1:8" ht="78" customHeight="1">
       <c r="A174" s="23" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B174" s="24" t="s">
         <v>611</v>
@@ -47963,7 +47960,7 @@
     </row>
     <row r="175" spans="1:8" ht="78" customHeight="1">
       <c r="A175" s="23" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B175" s="24" t="s">
         <v>613</v>
@@ -47985,7 +47982,7 @@
     </row>
     <row r="176" spans="1:8" ht="78" customHeight="1">
       <c r="A176" s="23" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B176" s="24" t="s">
         <v>617</v>
@@ -48007,7 +48004,7 @@
     </row>
     <row r="177" spans="1:8" ht="78" customHeight="1">
       <c r="A177" s="23" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B177" s="24" t="s">
         <v>619</v>
@@ -48029,13 +48026,13 @@
     </row>
     <row r="178" spans="1:8" ht="78" customHeight="1">
       <c r="A178" s="23" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B178" s="24" t="s">
         <v>622</v>
       </c>
       <c r="C178" s="24" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="D178" s="25">
         <v>400000</v>
@@ -48051,7 +48048,7 @@
     </row>
     <row r="179" spans="1:8" ht="78" customHeight="1">
       <c r="A179" s="23" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B179" s="24" t="s">
         <v>624</v>
@@ -48073,7 +48070,7 @@
     </row>
     <row r="180" spans="1:8" ht="78" customHeight="1">
       <c r="A180" s="23" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B180" s="24" t="s">
         <v>627</v>
@@ -48551,7 +48548,7 @@
         <v>677</v>
       </c>
       <c r="C200" s="30" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="D200" s="25"/>
       <c r="E200" s="25"/>
@@ -48567,7 +48564,7 @@
         <v>678</v>
       </c>
       <c r="C201" s="24" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="D201" s="25"/>
       <c r="E201" s="25"/>
@@ -48577,7 +48574,7 @@
     </row>
     <row r="202" spans="1:8" ht="78" customHeight="1">
       <c r="A202" s="23" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="B202" s="24" t="s">
         <v>680</v>
@@ -48603,7 +48600,7 @@
     </row>
     <row r="203" spans="1:8" ht="78" customHeight="1">
       <c r="A203" s="23" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="B203" s="24" t="s">
         <v>682</v>
@@ -48627,7 +48624,7 @@
     </row>
     <row r="204" spans="1:8" ht="78" customHeight="1">
       <c r="A204" s="23" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="B204" s="24" t="s">
         <v>684</v>
@@ -48649,7 +48646,7 @@
     </row>
     <row r="205" spans="1:8" ht="78" customHeight="1">
       <c r="A205" s="23" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="B205" s="24" t="s">
         <v>687</v>
@@ -48671,7 +48668,7 @@
     </row>
     <row r="206" spans="1:8" ht="78" customHeight="1">
       <c r="A206" s="23" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="B206" s="24" t="s">
         <v>689</v>
@@ -48693,7 +48690,7 @@
     </row>
     <row r="207" spans="1:8" ht="78" customHeight="1">
       <c r="A207" s="23" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="B207" s="24" t="s">
         <v>691</v>
@@ -48713,7 +48710,7 @@
     </row>
     <row r="208" spans="1:8" ht="78" customHeight="1">
       <c r="A208" s="23" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="B208" s="24" t="s">
         <v>694</v>
@@ -48733,7 +48730,7 @@
     </row>
     <row r="209" spans="1:8" ht="78" customHeight="1">
       <c r="A209" s="23" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="B209" s="24" t="s">
         <v>696</v>
@@ -48753,7 +48750,7 @@
     </row>
     <row r="210" spans="1:8" ht="78" customHeight="1">
       <c r="A210" s="23" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B210" s="24" t="s">
         <v>423</v>
@@ -48773,7 +48770,7 @@
     </row>
     <row r="211" spans="1:8" ht="78" customHeight="1">
       <c r="A211" s="23" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B211" s="24" t="s">
         <v>424</v>
@@ -48793,7 +48790,7 @@
     </row>
     <row r="212" spans="1:8" ht="78" customHeight="1">
       <c r="A212" s="23" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B212" s="24" t="s">
         <v>426</v>
@@ -48813,7 +48810,7 @@
     </row>
     <row r="213" spans="1:8" ht="78" customHeight="1">
       <c r="A213" s="23" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B213" s="24" t="s">
         <v>429</v>
@@ -48833,7 +48830,7 @@
     </row>
     <row r="214" spans="1:8" ht="78" customHeight="1">
       <c r="A214" s="23" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B214" s="24" t="s">
         <v>431</v>
@@ -48853,7 +48850,7 @@
     </row>
     <row r="215" spans="1:8" ht="78" customHeight="1">
       <c r="A215" s="23" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B215" s="24" t="s">
         <v>433</v>
@@ -48873,7 +48870,7 @@
     </row>
     <row r="216" spans="1:8" ht="78" customHeight="1">
       <c r="A216" s="23" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B216" s="24" t="s">
         <v>435</v>
@@ -48893,7 +48890,7 @@
     </row>
     <row r="217" spans="1:8" ht="78" customHeight="1">
       <c r="A217" s="23" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="B217" s="24" t="s">
         <v>700</v>
@@ -48919,7 +48916,7 @@
     </row>
     <row r="218" spans="1:8" ht="78" customHeight="1">
       <c r="A218" s="23" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="B218" s="24" t="s">
         <v>704</v>
@@ -48945,7 +48942,7 @@
     </row>
     <row r="219" spans="1:8" ht="78" customHeight="1">
       <c r="A219" s="23" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="B219" s="24" t="s">
         <v>708</v>
@@ -48971,7 +48968,7 @@
     </row>
     <row r="220" spans="1:8" ht="78" customHeight="1">
       <c r="A220" s="23" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="B220" s="24" t="s">
         <v>710</v>
@@ -48997,7 +48994,7 @@
     </row>
     <row r="221" spans="1:8" ht="78" customHeight="1">
       <c r="A221" s="23" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="B221" s="24" t="s">
         <v>712</v>
@@ -49023,7 +49020,7 @@
     </row>
     <row r="222" spans="1:8" ht="78" customHeight="1">
       <c r="A222" s="23" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B222" s="24" t="s">
         <v>715</v>
@@ -49049,7 +49046,7 @@
     </row>
     <row r="223" spans="1:8" ht="78" customHeight="1">
       <c r="A223" s="23" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B223" s="24" t="s">
         <v>719</v>
@@ -49075,7 +49072,7 @@
     </row>
     <row r="224" spans="1:8" ht="78" customHeight="1">
       <c r="A224" s="23" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="B224" s="24" t="s">
         <v>723</v>
@@ -49101,7 +49098,7 @@
     </row>
     <row r="225" spans="1:8" ht="78" customHeight="1">
       <c r="A225" s="23" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="B225" s="24" t="s">
         <v>725</v>
@@ -49127,7 +49124,7 @@
     </row>
     <row r="226" spans="1:8" ht="78" customHeight="1">
       <c r="A226" s="23" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="B226" s="24" t="s">
         <v>727</v>
@@ -49156,7 +49153,7 @@
         <v>729</v>
       </c>
       <c r="B227" s="24" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="C227" s="24" t="s">
         <v>731</v>
@@ -49182,7 +49179,7 @@
         <v>729</v>
       </c>
       <c r="B228" s="24" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="C228" s="24" t="s">
         <v>734</v>
@@ -49205,7 +49202,7 @@
     </row>
     <row r="229" spans="1:8" ht="78" customHeight="1">
       <c r="A229" s="23" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="B229" s="24" t="s">
         <v>737</v>
@@ -49227,7 +49224,7 @@
     </row>
     <row r="230" spans="1:8" ht="78" customHeight="1">
       <c r="A230" s="23" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="B230" s="24" t="s">
         <v>741</v>
@@ -49247,7 +49244,7 @@
     </row>
     <row r="231" spans="1:8" ht="78" customHeight="1">
       <c r="A231" s="23" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="B231" s="24" t="s">
         <v>745</v>
@@ -49269,7 +49266,7 @@
     </row>
     <row r="232" spans="1:8" ht="78" customHeight="1">
       <c r="A232" s="23" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="B232" s="24" t="s">
         <v>749</v>
@@ -49289,7 +49286,7 @@
     </row>
     <row r="233" spans="1:8" ht="78" customHeight="1">
       <c r="A233" s="23" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="B233" s="24" t="s">
         <v>753</v>
@@ -49311,7 +49308,7 @@
     </row>
     <row r="234" spans="1:8" ht="78" customHeight="1">
       <c r="A234" s="23" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="B234" s="24" t="s">
         <v>757</v>
@@ -49333,7 +49330,7 @@
     </row>
     <row r="235" spans="1:8" ht="78" customHeight="1">
       <c r="A235" s="23" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B235" s="24" t="s">
         <v>761</v>
@@ -49359,7 +49356,7 @@
     </row>
     <row r="236" spans="1:8" ht="78" customHeight="1">
       <c r="A236" s="23" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B236" s="24" t="s">
         <v>765</v>
@@ -49385,7 +49382,7 @@
     </row>
     <row r="237" spans="1:8" ht="78" customHeight="1">
       <c r="A237" s="23" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="B237" s="24" t="s">
         <v>768</v>
@@ -49411,7 +49408,7 @@
     </row>
     <row r="238" spans="1:8" ht="78" customHeight="1">
       <c r="A238" s="23" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="B238" s="24" t="s">
         <v>771</v>
@@ -49437,7 +49434,7 @@
     </row>
     <row r="239" spans="1:8" ht="78" customHeight="1">
       <c r="A239" s="23" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="B239" s="24" t="s">
         <v>773</v>
@@ -49463,7 +49460,7 @@
     </row>
     <row r="240" spans="1:8" ht="78" customHeight="1">
       <c r="A240" s="23" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="B240" s="24" t="s">
         <v>775</v>
@@ -49489,7 +49486,7 @@
     </row>
     <row r="241" spans="1:8" ht="78" customHeight="1">
       <c r="A241" s="23" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="B241" s="24" t="s">
         <v>777</v>
@@ -49583,7 +49580,7 @@
         <v>790</v>
       </c>
       <c r="C245" s="24" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="D245" s="25">
         <v>1000000</v>
@@ -49609,7 +49606,7 @@
         <v>792</v>
       </c>
       <c r="C246" s="24" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="D246" s="25">
         <v>400000</v>
@@ -49635,7 +49632,7 @@
         <v>793</v>
       </c>
       <c r="C247" s="24" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="D247" s="25">
         <v>400000</v>
@@ -49661,7 +49658,7 @@
         <v>795</v>
       </c>
       <c r="C248" s="24" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="D248" s="25">
         <v>600000</v>
@@ -49767,7 +49764,7 @@
     </row>
     <row r="253" spans="1:8" ht="78" customHeight="1">
       <c r="A253" s="23" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B253" s="24" t="s">
         <v>811</v>
@@ -49793,7 +49790,7 @@
     </row>
     <row r="254" spans="1:8" ht="78" customHeight="1">
       <c r="A254" s="23" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B254" s="24" t="s">
         <v>813</v>
@@ -49819,7 +49816,7 @@
     </row>
     <row r="255" spans="1:8" ht="78" customHeight="1">
       <c r="A255" s="23" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B255" s="24" t="s">
         <v>815</v>
@@ -49845,7 +49842,7 @@
     </row>
     <row r="256" spans="1:8" ht="78" customHeight="1">
       <c r="A256" s="23" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B256" s="24" t="s">
         <v>817</v>
@@ -49871,7 +49868,7 @@
     </row>
     <row r="257" spans="1:8" ht="78" customHeight="1">
       <c r="A257" s="23" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B257" s="24" t="s">
         <v>819</v>
@@ -49897,7 +49894,7 @@
     </row>
     <row r="258" spans="1:8" ht="78" customHeight="1">
       <c r="A258" s="23" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="B258" s="24" t="s">
         <v>822</v>
@@ -49923,7 +49920,7 @@
     </row>
     <row r="259" spans="1:8" ht="78" customHeight="1">
       <c r="A259" s="23" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="B259" s="24" t="s">
         <v>824</v>
@@ -50048,7 +50045,7 @@
         <v>826</v>
       </c>
       <c r="B264" s="24" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="C264" s="24" t="s">
         <v>839</v>
@@ -50091,7 +50088,7 @@
     </row>
     <row r="266" spans="1:8" ht="78" customHeight="1">
       <c r="A266" s="23" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="B266" s="24" t="s">
         <v>842</v>
@@ -50117,7 +50114,7 @@
     </row>
     <row r="267" spans="1:8" ht="78" customHeight="1">
       <c r="A267" s="23" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="B267" s="24" t="s">
         <v>844</v>
@@ -50143,7 +50140,7 @@
     </row>
     <row r="268" spans="1:8" ht="78" customHeight="1">
       <c r="A268" s="23" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B268" s="24" t="s">
         <v>848</v>
@@ -50169,7 +50166,7 @@
     </row>
     <row r="269" spans="1:8" ht="78" customHeight="1">
       <c r="A269" s="23" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B269" s="24" t="s">
         <v>850</v>
@@ -50195,7 +50192,7 @@
     </row>
     <row r="270" spans="1:8" ht="78" customHeight="1">
       <c r="A270" s="23" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B270" s="24" t="s">
         <v>853</v>
@@ -50221,7 +50218,7 @@
     </row>
     <row r="271" spans="1:8" ht="78" customHeight="1">
       <c r="A271" s="23" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B271" s="24" t="s">
         <v>854</v>
@@ -50247,13 +50244,13 @@
     </row>
     <row r="272" spans="1:8" ht="78" customHeight="1">
       <c r="A272" s="23" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B272" s="24" t="s">
         <v>856</v>
       </c>
       <c r="C272" s="24" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="D272" s="25">
         <v>400000</v>
@@ -50273,7 +50270,7 @@
     </row>
     <row r="273" spans="1:8" ht="78" customHeight="1">
       <c r="A273" s="23" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B273" s="24" t="s">
         <v>857</v>
@@ -50299,7 +50296,7 @@
     </row>
     <row r="274" spans="1:8" ht="78" customHeight="1">
       <c r="A274" s="23" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B274" s="24" t="s">
         <v>859</v>
@@ -50325,7 +50322,7 @@
     </row>
     <row r="275" spans="1:8" ht="78" customHeight="1">
       <c r="A275" s="23" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="B275" s="24" t="s">
         <v>861</v>
@@ -50347,7 +50344,7 @@
     </row>
     <row r="276" spans="1:8" ht="78" customHeight="1">
       <c r="A276" s="23" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="B276" s="24" t="s">
         <v>864</v>
@@ -50583,7 +50580,7 @@
     </row>
     <row r="286" spans="1:8" ht="78" customHeight="1">
       <c r="A286" s="23" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="B286" s="24" t="s">
         <v>867</v>
@@ -50609,7 +50606,7 @@
     </row>
     <row r="287" spans="1:8" ht="78" customHeight="1">
       <c r="A287" s="23" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="B287" s="24" t="s">
         <v>871</v>
